--- a/tiflow/audit-event-profile/2.0.0-ballot.2/StructureDefinition-tiflow-order-task.xlsx
+++ b/tiflow/audit-event-profile/2.0.0-ballot.2/StructureDefinition-tiflow-order-task.xlsx
@@ -16,7 +16,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="2664" uniqueCount="505">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="2679" uniqueCount="520">
   <si>
     <t>Property</t>
   </si>
@@ -483,6 +483,16 @@
     <t>Meta.security</t>
   </si>
   <si>
+    <t xml:space="preserve">ele-1
+</t>
+  </si>
+  <si>
+    <t>CV</t>
+  </si>
+  <si>
+    <t>CE/CNE/CWE subset one of the sets of component 1-3 or 4-6</t>
+  </si>
+  <si>
     <t>Task.meta.tag</t>
   </si>
   <si>
@@ -653,6 +663,9 @@
     <t>FiveWs.identifier</t>
   </si>
   <si>
+    <t>CX / EI (occasionally, more often EI maps to a resource id or a URL)</t>
+  </si>
+  <si>
     <t>Task.identifier:AccessCode</t>
   </si>
   <si>
@@ -692,6 +705,9 @@
     <t>The URL pointing to a *FHIR*-defined protocol, guideline, orderset or other definition that is adhered to in whole or in part by this Task.</t>
   </si>
   <si>
+    <t>see [Canonical References](http://hl7.org/fhir/R4/references.html#canonical)</t>
+  </si>
+  <si>
     <t>Enables a formal definition of how he task is to be performed, enabling automation.</t>
   </si>
   <si>
@@ -705,6 +721,9 @@
   </si>
   <si>
     <t>The URL pointing to an *externally* maintained  protocol, guideline, orderset or other definition that is adhered to in whole or in part by this Task.</t>
+  </si>
+  <si>
+    <t>see http://en.wikipedia.org/wiki/Uniform_resource_identifier</t>
   </si>
   <si>
     <t>Enables a formal definition of how he task is to be performed (e.g. using BPMN, BPEL, XPDL or other formal notation to be associated with a task), enabling automation.</t>
@@ -726,6 +745,13 @@
     <t>BasedOn refers to a higher-level authorization that triggered the creation of the task.  It references a "request" resource such as a ServiceRequest, MedicationRequest, ServiceRequest, CarePlan, etc. which is distinct from the "request" resource the task is seeking to fulfill.  This latter resource is referenced by FocusOn.  For example, based on a ServiceRequest (= BasedOn), a task is created to fulfill a procedureRequest ( = FocusOn ) to collect a specimen from a patient.</t>
   </si>
   <si>
+    <t>References SHALL be a reference to an actual FHIR resource, and SHALL be resolveable (allowing for access control, temporary unavailability, etc.). Resolution can be either by retrieval from the URL, or, where applicable by resource type, by treating an absolute reference as a canonical URL and looking it up in a local registry/repository.</t>
+  </si>
+  <si>
+    <t>ele-1:All FHIR elements must have a @value or children {hasValue() or (children().count() &gt; id.count())}
+ref-1:SHALL have a contained resource if a local reference is provided {reference.startsWith('#').not() or (reference.substring(1).trace('url') in %rootResource.contained.id.trace('ids'))}</t>
+  </si>
+  <si>
     <t>Request.basedOn, Event.basedOn</t>
   </si>
   <si>
@@ -824,6 +850,9 @@
     <t>.inboundRelationship[typeCode=SUBJ].source[classCode=CACT, moodCode=EVN, code="status change"].reasonCode</t>
   </si>
   <si>
+    <t>CE/CNE/CWE</t>
+  </si>
+  <si>
     <t>Task.businessStatus</t>
   </si>
   <si>
@@ -831,6 +860,9 @@
   </si>
   <si>
     <t>Contains business-specific nuances of the business state.</t>
+  </si>
+  <si>
+    <t>Not all terminology uses fit this general pattern. In some cases, models should not use CodeableConcept and use Coding directly and provide their own structure for managing text, codings, translations and the relationship between elements and pre- and post-coordination.</t>
   </si>
   <si>
     <t>There's often a need to track substates of a task - this is often variable by specific workflow implementation.</t>
@@ -937,6 +969,9 @@
   </si>
   <si>
     <t>A free-text description of what is to be performed.</t>
+  </si>
+  <si>
+    <t>Note that FHIR strings SHALL NOT exceed 1MB in size</t>
   </si>
   <si>
     <t>.text</t>
@@ -1110,6 +1145,14 @@
     <t>Identifies the time action was first taken against the task (start) and/or the time final action was taken against the task prior to marking it as completed (end).</t>
   </si>
   <si>
+    <t>A Period specifies a range of time; the context of use will specify whether the entire range applies (e.g. "the patient was an inpatient of the hospital for this time range") or one value from the range applies (e.g. "give to the patient between these two times").
+Period is not used for a duration (a measure of elapsed time). See [Duration](http://hl7.org/fhir/R4/datatypes.html#Duration).</t>
+  </si>
+  <si>
+    <t>ele-1:All FHIR elements must have a @value or children {hasValue() or (children().count() &gt; id.count())}
+per-1:If present, start SHALL have a lower value than end {start.hasValue().not() or end.hasValue().not() or (start &lt;= end)}</t>
+  </si>
+  <si>
     <t>Event.occurrence[x]</t>
   </si>
   <si>
@@ -1117,6 +1160,9 @@
   </si>
   <si>
     <t>FiveWs.done[x]</t>
+  </si>
+  <si>
+    <t>DR</t>
   </si>
   <si>
     <t>Task.authoredOn</t>
@@ -1352,6 +1398,9 @@
   </si>
   <si>
     <t>Free-text information captured about the task as it progresses.</t>
+  </si>
+  <si>
+    <t>For systems that do not have structured annotations, they can simply communicate a single annotation with no author or time.  This element may need to be included in narrative because of the potential for modifying information.  *Annotations SHOULD NOT* be used to communicate "modifying" information that could be computable. (This is a SHOULD because enforcing user behavior is nearly impossible).</t>
   </si>
   <si>
     <t>Request.note, Event.note</t>
@@ -1951,7 +2000,7 @@
     <col min="37" max="37" width="47.7734375" customWidth="true" bestFit="true"/>
     <col min="38" max="38" width="94.296875" customWidth="true" bestFit="true"/>
     <col min="39" max="39" width="31.65234375" customWidth="true" bestFit="true"/>
-    <col min="40" max="40" width="24.1328125" customWidth="true" bestFit="true"/>
+    <col min="40" max="40" width="53.91015625" customWidth="true" bestFit="true"/>
   </cols>
   <sheetData>
     <row r="1">
@@ -3192,7 +3241,7 @@
         <v>80</v>
       </c>
       <c r="AI11" t="s" s="2">
-        <v>78</v>
+        <v>150</v>
       </c>
       <c r="AJ11" t="s" s="2">
         <v>100</v>
@@ -3201,21 +3250,21 @@
         <v>78</v>
       </c>
       <c r="AL11" t="s" s="2">
-        <v>78</v>
+        <v>151</v>
       </c>
       <c r="AM11" t="s" s="2">
         <v>78</v>
       </c>
       <c r="AN11" t="s" s="2">
-        <v>78</v>
+        <v>152</v>
       </c>
     </row>
     <row r="12" hidden="true">
       <c r="A12" t="s" s="2">
-        <v>150</v>
+        <v>153</v>
       </c>
       <c r="B12" t="s" s="2">
-        <v>150</v>
+        <v>153</v>
       </c>
       <c r="C12" s="2"/>
       <c r="D12" t="s" s="2">
@@ -3241,13 +3290,13 @@
         <v>142</v>
       </c>
       <c r="L12" t="s" s="2">
-        <v>151</v>
+        <v>154</v>
       </c>
       <c r="M12" t="s" s="2">
-        <v>152</v>
+        <v>155</v>
       </c>
       <c r="N12" t="s" s="2">
-        <v>153</v>
+        <v>156</v>
       </c>
       <c r="O12" s="2"/>
       <c r="P12" t="s" s="2">
@@ -3273,13 +3322,13 @@
         <v>78</v>
       </c>
       <c r="X12" t="s" s="2">
-        <v>154</v>
+        <v>157</v>
       </c>
       <c r="Y12" t="s" s="2">
-        <v>155</v>
+        <v>158</v>
       </c>
       <c r="Z12" t="s" s="2">
-        <v>156</v>
+        <v>159</v>
       </c>
       <c r="AA12" t="s" s="2">
         <v>78</v>
@@ -3297,7 +3346,7 @@
         <v>78</v>
       </c>
       <c r="AF12" t="s" s="2">
-        <v>157</v>
+        <v>160</v>
       </c>
       <c r="AG12" t="s" s="2">
         <v>79</v>
@@ -3306,7 +3355,7 @@
         <v>80</v>
       </c>
       <c r="AI12" t="s" s="2">
-        <v>78</v>
+        <v>150</v>
       </c>
       <c r="AJ12" t="s" s="2">
         <v>100</v>
@@ -3315,21 +3364,21 @@
         <v>78</v>
       </c>
       <c r="AL12" t="s" s="2">
-        <v>78</v>
+        <v>151</v>
       </c>
       <c r="AM12" t="s" s="2">
         <v>78</v>
       </c>
       <c r="AN12" t="s" s="2">
-        <v>78</v>
+        <v>152</v>
       </c>
     </row>
     <row r="13" hidden="true">
       <c r="A13" t="s" s="2">
-        <v>158</v>
+        <v>161</v>
       </c>
       <c r="B13" t="s" s="2">
-        <v>158</v>
+        <v>161</v>
       </c>
       <c r="C13" s="2"/>
       <c r="D13" t="s" s="2">
@@ -3355,13 +3404,13 @@
         <v>130</v>
       </c>
       <c r="L13" t="s" s="2">
-        <v>159</v>
+        <v>162</v>
       </c>
       <c r="M13" t="s" s="2">
-        <v>160</v>
+        <v>163</v>
       </c>
       <c r="N13" t="s" s="2">
-        <v>161</v>
+        <v>164</v>
       </c>
       <c r="O13" s="2"/>
       <c r="P13" t="s" s="2">
@@ -3411,7 +3460,7 @@
         <v>78</v>
       </c>
       <c r="AF13" t="s" s="2">
-        <v>162</v>
+        <v>165</v>
       </c>
       <c r="AG13" t="s" s="2">
         <v>79</v>
@@ -3440,10 +3489,10 @@
     </row>
     <row r="14" hidden="true">
       <c r="A14" t="s" s="2">
-        <v>163</v>
+        <v>166</v>
       </c>
       <c r="B14" t="s" s="2">
-        <v>163</v>
+        <v>166</v>
       </c>
       <c r="C14" s="2"/>
       <c r="D14" t="s" s="2">
@@ -3466,16 +3515,16 @@
         <v>78</v>
       </c>
       <c r="K14" t="s" s="2">
-        <v>164</v>
+        <v>167</v>
       </c>
       <c r="L14" t="s" s="2">
-        <v>165</v>
+        <v>168</v>
       </c>
       <c r="M14" t="s" s="2">
-        <v>166</v>
+        <v>169</v>
       </c>
       <c r="N14" t="s" s="2">
-        <v>167</v>
+        <v>170</v>
       </c>
       <c r="O14" s="2"/>
       <c r="P14" t="s" s="2">
@@ -3501,13 +3550,13 @@
         <v>78</v>
       </c>
       <c r="X14" t="s" s="2">
-        <v>168</v>
+        <v>171</v>
       </c>
       <c r="Y14" t="s" s="2">
-        <v>169</v>
+        <v>172</v>
       </c>
       <c r="Z14" t="s" s="2">
-        <v>170</v>
+        <v>173</v>
       </c>
       <c r="AA14" t="s" s="2">
         <v>78</v>
@@ -3525,7 +3574,7 @@
         <v>78</v>
       </c>
       <c r="AF14" t="s" s="2">
-        <v>171</v>
+        <v>174</v>
       </c>
       <c r="AG14" t="s" s="2">
         <v>79</v>
@@ -3554,14 +3603,14 @@
     </row>
     <row r="15" hidden="true">
       <c r="A15" t="s" s="2">
-        <v>172</v>
+        <v>175</v>
       </c>
       <c r="B15" t="s" s="2">
-        <v>172</v>
+        <v>175</v>
       </c>
       <c r="C15" s="2"/>
       <c r="D15" t="s" s="2">
-        <v>173</v>
+        <v>176</v>
       </c>
       <c r="E15" s="2"/>
       <c r="F15" t="s" s="2">
@@ -3580,16 +3629,16 @@
         <v>78</v>
       </c>
       <c r="K15" t="s" s="2">
-        <v>174</v>
+        <v>177</v>
       </c>
       <c r="L15" t="s" s="2">
-        <v>175</v>
+        <v>178</v>
       </c>
       <c r="M15" t="s" s="2">
-        <v>176</v>
+        <v>179</v>
       </c>
       <c r="N15" t="s" s="2">
-        <v>177</v>
+        <v>180</v>
       </c>
       <c r="O15" s="2"/>
       <c r="P15" t="s" s="2">
@@ -3639,7 +3688,7 @@
         <v>78</v>
       </c>
       <c r="AF15" t="s" s="2">
-        <v>178</v>
+        <v>181</v>
       </c>
       <c r="AG15" t="s" s="2">
         <v>79</v>
@@ -3657,7 +3706,7 @@
         <v>78</v>
       </c>
       <c r="AL15" t="s" s="2">
-        <v>179</v>
+        <v>182</v>
       </c>
       <c r="AM15" t="s" s="2">
         <v>78</v>
@@ -3668,14 +3717,14 @@
     </row>
     <row r="16" hidden="true">
       <c r="A16" t="s" s="2">
-        <v>180</v>
+        <v>183</v>
       </c>
       <c r="B16" t="s" s="2">
-        <v>180</v>
+        <v>183</v>
       </c>
       <c r="C16" s="2"/>
       <c r="D16" t="s" s="2">
-        <v>181</v>
+        <v>184</v>
       </c>
       <c r="E16" s="2"/>
       <c r="F16" t="s" s="2">
@@ -3694,16 +3743,16 @@
         <v>78</v>
       </c>
       <c r="K16" t="s" s="2">
-        <v>182</v>
+        <v>185</v>
       </c>
       <c r="L16" t="s" s="2">
-        <v>183</v>
+        <v>186</v>
       </c>
       <c r="M16" t="s" s="2">
-        <v>184</v>
+        <v>187</v>
       </c>
       <c r="N16" t="s" s="2">
-        <v>185</v>
+        <v>188</v>
       </c>
       <c r="O16" s="2"/>
       <c r="P16" t="s" s="2">
@@ -3753,7 +3802,7 @@
         <v>78</v>
       </c>
       <c r="AF16" t="s" s="2">
-        <v>186</v>
+        <v>189</v>
       </c>
       <c r="AG16" t="s" s="2">
         <v>79</v>
@@ -3771,7 +3820,7 @@
         <v>78</v>
       </c>
       <c r="AL16" t="s" s="2">
-        <v>187</v>
+        <v>190</v>
       </c>
       <c r="AM16" t="s" s="2">
         <v>78</v>
@@ -3782,10 +3831,10 @@
     </row>
     <row r="17" hidden="true">
       <c r="A17" t="s" s="2">
-        <v>188</v>
+        <v>191</v>
       </c>
       <c r="B17" t="s" s="2">
-        <v>188</v>
+        <v>191</v>
       </c>
       <c r="C17" s="2"/>
       <c r="D17" t="s" s="2">
@@ -3814,7 +3863,7 @@
         <v>110</v>
       </c>
       <c r="M17" t="s" s="2">
-        <v>189</v>
+        <v>192</v>
       </c>
       <c r="N17" t="s" s="2">
         <v>112</v>
@@ -3855,19 +3904,19 @@
         <v>78</v>
       </c>
       <c r="AB17" t="s" s="2">
-        <v>78</v>
+        <v>113</v>
       </c>
       <c r="AC17" t="s" s="2">
-        <v>78</v>
+        <v>114</v>
       </c>
       <c r="AD17" t="s" s="2">
         <v>78</v>
       </c>
       <c r="AE17" t="s" s="2">
-        <v>78</v>
+        <v>115</v>
       </c>
       <c r="AF17" t="s" s="2">
-        <v>190</v>
+        <v>193</v>
       </c>
       <c r="AG17" t="s" s="2">
         <v>79</v>
@@ -3885,7 +3934,7 @@
         <v>78</v>
       </c>
       <c r="AL17" t="s" s="2">
-        <v>187</v>
+        <v>190</v>
       </c>
       <c r="AM17" t="s" s="2">
         <v>78</v>
@@ -3896,10 +3945,10 @@
     </row>
     <row r="18" hidden="true">
       <c r="A18" t="s" s="2">
-        <v>191</v>
+        <v>194</v>
       </c>
       <c r="B18" t="s" s="2">
-        <v>191</v>
+        <v>194</v>
       </c>
       <c r="C18" s="2"/>
       <c r="D18" t="s" s="2">
@@ -3925,16 +3974,16 @@
         <v>109</v>
       </c>
       <c r="L18" t="s" s="2">
-        <v>192</v>
+        <v>195</v>
       </c>
       <c r="M18" t="s" s="2">
-        <v>193</v>
+        <v>196</v>
       </c>
       <c r="N18" t="s" s="2">
         <v>112</v>
       </c>
       <c r="O18" t="s" s="2">
-        <v>194</v>
+        <v>197</v>
       </c>
       <c r="P18" t="s" s="2">
         <v>78</v>
@@ -3971,19 +4020,19 @@
         <v>78</v>
       </c>
       <c r="AB18" t="s" s="2">
-        <v>78</v>
+        <v>113</v>
       </c>
       <c r="AC18" t="s" s="2">
-        <v>78</v>
+        <v>114</v>
       </c>
       <c r="AD18" t="s" s="2">
         <v>78</v>
       </c>
       <c r="AE18" t="s" s="2">
-        <v>78</v>
+        <v>115</v>
       </c>
       <c r="AF18" t="s" s="2">
-        <v>195</v>
+        <v>198</v>
       </c>
       <c r="AG18" t="s" s="2">
         <v>79</v>
@@ -4001,7 +4050,7 @@
         <v>78</v>
       </c>
       <c r="AL18" t="s" s="2">
-        <v>187</v>
+        <v>190</v>
       </c>
       <c r="AM18" t="s" s="2">
         <v>78</v>
@@ -4012,10 +4061,10 @@
     </row>
     <row r="19" hidden="true">
       <c r="A19" t="s" s="2">
-        <v>196</v>
+        <v>199</v>
       </c>
       <c r="B19" t="s" s="2">
-        <v>196</v>
+        <v>199</v>
       </c>
       <c r="C19" s="2"/>
       <c r="D19" t="s" s="2">
@@ -4038,13 +4087,13 @@
         <v>78</v>
       </c>
       <c r="K19" t="s" s="2">
-        <v>197</v>
+        <v>200</v>
       </c>
       <c r="L19" t="s" s="2">
-        <v>198</v>
+        <v>201</v>
       </c>
       <c r="M19" t="s" s="2">
-        <v>199</v>
+        <v>202</v>
       </c>
       <c r="N19" s="2"/>
       <c r="O19" s="2"/>
@@ -4083,7 +4132,7 @@
         <v>78</v>
       </c>
       <c r="AB19" t="s" s="2">
-        <v>200</v>
+        <v>203</v>
       </c>
       <c r="AC19" s="2"/>
       <c r="AD19" t="s" s="2">
@@ -4093,7 +4142,7 @@
         <v>115</v>
       </c>
       <c r="AF19" t="s" s="2">
-        <v>196</v>
+        <v>199</v>
       </c>
       <c r="AG19" t="s" s="2">
         <v>79</v>
@@ -4102,33 +4151,33 @@
         <v>80</v>
       </c>
       <c r="AI19" t="s" s="2">
-        <v>78</v>
+        <v>150</v>
       </c>
       <c r="AJ19" t="s" s="2">
         <v>100</v>
       </c>
       <c r="AK19" t="s" s="2">
-        <v>201</v>
+        <v>204</v>
       </c>
       <c r="AL19" t="s" s="2">
-        <v>202</v>
+        <v>205</v>
       </c>
       <c r="AM19" t="s" s="2">
-        <v>203</v>
+        <v>206</v>
       </c>
       <c r="AN19" t="s" s="2">
-        <v>78</v>
+        <v>207</v>
       </c>
     </row>
     <row r="20" hidden="true">
       <c r="A20" t="s" s="2">
-        <v>204</v>
+        <v>208</v>
       </c>
       <c r="B20" t="s" s="2">
-        <v>196</v>
+        <v>199</v>
       </c>
       <c r="C20" t="s" s="2">
-        <v>205</v>
+        <v>209</v>
       </c>
       <c r="D20" t="s" s="2">
         <v>78</v>
@@ -4150,13 +4199,13 @@
         <v>78</v>
       </c>
       <c r="K20" t="s" s="2">
-        <v>206</v>
+        <v>210</v>
       </c>
       <c r="L20" t="s" s="2">
-        <v>207</v>
+        <v>211</v>
       </c>
       <c r="M20" t="s" s="2">
-        <v>208</v>
+        <v>212</v>
       </c>
       <c r="N20" s="2"/>
       <c r="O20" s="2"/>
@@ -4207,7 +4256,7 @@
         <v>78</v>
       </c>
       <c r="AF20" t="s" s="2">
-        <v>196</v>
+        <v>199</v>
       </c>
       <c r="AG20" t="s" s="2">
         <v>79</v>
@@ -4216,33 +4265,33 @@
         <v>80</v>
       </c>
       <c r="AI20" t="s" s="2">
-        <v>78</v>
+        <v>150</v>
       </c>
       <c r="AJ20" t="s" s="2">
         <v>100</v>
       </c>
       <c r="AK20" t="s" s="2">
-        <v>201</v>
+        <v>204</v>
       </c>
       <c r="AL20" t="s" s="2">
-        <v>202</v>
+        <v>205</v>
       </c>
       <c r="AM20" t="s" s="2">
-        <v>203</v>
+        <v>206</v>
       </c>
       <c r="AN20" t="s" s="2">
-        <v>78</v>
+        <v>207</v>
       </c>
     </row>
     <row r="21" hidden="true">
       <c r="A21" t="s" s="2">
-        <v>209</v>
+        <v>213</v>
       </c>
       <c r="B21" t="s" s="2">
-        <v>196</v>
+        <v>199</v>
       </c>
       <c r="C21" t="s" s="2">
-        <v>210</v>
+        <v>214</v>
       </c>
       <c r="D21" t="s" s="2">
         <v>78</v>
@@ -4264,13 +4313,13 @@
         <v>78</v>
       </c>
       <c r="K21" t="s" s="2">
-        <v>211</v>
+        <v>215</v>
       </c>
       <c r="L21" t="s" s="2">
-        <v>210</v>
+        <v>214</v>
       </c>
       <c r="M21" t="s" s="2">
-        <v>199</v>
+        <v>202</v>
       </c>
       <c r="N21" s="2"/>
       <c r="O21" s="2"/>
@@ -4321,7 +4370,7 @@
         <v>78</v>
       </c>
       <c r="AF21" t="s" s="2">
-        <v>196</v>
+        <v>199</v>
       </c>
       <c r="AG21" t="s" s="2">
         <v>79</v>
@@ -4330,30 +4379,30 @@
         <v>80</v>
       </c>
       <c r="AI21" t="s" s="2">
-        <v>78</v>
+        <v>150</v>
       </c>
       <c r="AJ21" t="s" s="2">
         <v>100</v>
       </c>
       <c r="AK21" t="s" s="2">
-        <v>201</v>
+        <v>204</v>
       </c>
       <c r="AL21" t="s" s="2">
-        <v>202</v>
+        <v>205</v>
       </c>
       <c r="AM21" t="s" s="2">
-        <v>203</v>
+        <v>206</v>
       </c>
       <c r="AN21" t="s" s="2">
-        <v>78</v>
+        <v>207</v>
       </c>
     </row>
     <row r="22" hidden="true">
       <c r="A22" t="s" s="2">
-        <v>212</v>
+        <v>216</v>
       </c>
       <c r="B22" t="s" s="2">
-        <v>212</v>
+        <v>216</v>
       </c>
       <c r="C22" s="2"/>
       <c r="D22" t="s" s="2">
@@ -4376,17 +4425,19 @@
         <v>89</v>
       </c>
       <c r="K22" t="s" s="2">
-        <v>213</v>
+        <v>217</v>
       </c>
       <c r="L22" t="s" s="2">
-        <v>214</v>
+        <v>218</v>
       </c>
       <c r="M22" t="s" s="2">
-        <v>215</v>
-      </c>
-      <c r="N22" s="2"/>
+        <v>219</v>
+      </c>
+      <c r="N22" t="s" s="2">
+        <v>220</v>
+      </c>
       <c r="O22" t="s" s="2">
-        <v>216</v>
+        <v>221</v>
       </c>
       <c r="P22" t="s" s="2">
         <v>78</v>
@@ -4435,7 +4486,7 @@
         <v>78</v>
       </c>
       <c r="AF22" t="s" s="2">
-        <v>212</v>
+        <v>216</v>
       </c>
       <c r="AG22" t="s" s="2">
         <v>79</v>
@@ -4450,10 +4501,10 @@
         <v>100</v>
       </c>
       <c r="AK22" t="s" s="2">
-        <v>217</v>
+        <v>222</v>
       </c>
       <c r="AL22" t="s" s="2">
-        <v>218</v>
+        <v>223</v>
       </c>
       <c r="AM22" t="s" s="2">
         <v>78</v>
@@ -4464,10 +4515,10 @@
     </row>
     <row r="23" hidden="true">
       <c r="A23" t="s" s="2">
-        <v>219</v>
+        <v>224</v>
       </c>
       <c r="B23" t="s" s="2">
-        <v>219</v>
+        <v>224</v>
       </c>
       <c r="C23" s="2"/>
       <c r="D23" t="s" s="2">
@@ -4493,14 +4544,16 @@
         <v>130</v>
       </c>
       <c r="L23" t="s" s="2">
-        <v>214</v>
+        <v>218</v>
       </c>
       <c r="M23" t="s" s="2">
-        <v>220</v>
-      </c>
-      <c r="N23" s="2"/>
+        <v>225</v>
+      </c>
+      <c r="N23" t="s" s="2">
+        <v>226</v>
+      </c>
       <c r="O23" t="s" s="2">
-        <v>221</v>
+        <v>227</v>
       </c>
       <c r="P23" t="s" s="2">
         <v>78</v>
@@ -4549,7 +4602,7 @@
         <v>78</v>
       </c>
       <c r="AF23" t="s" s="2">
-        <v>219</v>
+        <v>224</v>
       </c>
       <c r="AG23" t="s" s="2">
         <v>79</v>
@@ -4564,10 +4617,10 @@
         <v>100</v>
       </c>
       <c r="AK23" t="s" s="2">
-        <v>222</v>
+        <v>228</v>
       </c>
       <c r="AL23" t="s" s="2">
-        <v>218</v>
+        <v>223</v>
       </c>
       <c r="AM23" t="s" s="2">
         <v>78</v>
@@ -4578,10 +4631,10 @@
     </row>
     <row r="24" hidden="true">
       <c r="A24" t="s" s="2">
-        <v>223</v>
+        <v>229</v>
       </c>
       <c r="B24" t="s" s="2">
-        <v>223</v>
+        <v>229</v>
       </c>
       <c r="C24" s="2"/>
       <c r="D24" t="s" s="2">
@@ -4604,15 +4657,17 @@
         <v>89</v>
       </c>
       <c r="K24" t="s" s="2">
-        <v>224</v>
+        <v>230</v>
       </c>
       <c r="L24" t="s" s="2">
-        <v>225</v>
+        <v>231</v>
       </c>
       <c r="M24" t="s" s="2">
-        <v>226</v>
-      </c>
-      <c r="N24" s="2"/>
+        <v>232</v>
+      </c>
+      <c r="N24" t="s" s="2">
+        <v>233</v>
+      </c>
       <c r="O24" s="2"/>
       <c r="P24" t="s" s="2">
         <v>78</v>
@@ -4661,7 +4716,7 @@
         <v>78</v>
       </c>
       <c r="AF24" t="s" s="2">
-        <v>223</v>
+        <v>229</v>
       </c>
       <c r="AG24" t="s" s="2">
         <v>79</v>
@@ -4670,16 +4725,16 @@
         <v>80</v>
       </c>
       <c r="AI24" t="s" s="2">
-        <v>78</v>
+        <v>150</v>
       </c>
       <c r="AJ24" t="s" s="2">
-        <v>100</v>
+        <v>234</v>
       </c>
       <c r="AK24" t="s" s="2">
-        <v>227</v>
+        <v>235</v>
       </c>
       <c r="AL24" t="s" s="2">
-        <v>228</v>
+        <v>236</v>
       </c>
       <c r="AM24" t="s" s="2">
         <v>78</v>
@@ -4690,10 +4745,10 @@
     </row>
     <row r="25" hidden="true">
       <c r="A25" t="s" s="2">
-        <v>229</v>
+        <v>237</v>
       </c>
       <c r="B25" t="s" s="2">
-        <v>229</v>
+        <v>237</v>
       </c>
       <c r="C25" s="2"/>
       <c r="D25" t="s" s="2">
@@ -4716,17 +4771,17 @@
         <v>89</v>
       </c>
       <c r="K25" t="s" s="2">
-        <v>197</v>
+        <v>200</v>
       </c>
       <c r="L25" t="s" s="2">
-        <v>230</v>
+        <v>238</v>
       </c>
       <c r="M25" t="s" s="2">
-        <v>231</v>
+        <v>239</v>
       </c>
       <c r="N25" s="2"/>
       <c r="O25" t="s" s="2">
-        <v>232</v>
+        <v>240</v>
       </c>
       <c r="P25" t="s" s="2">
         <v>78</v>
@@ -4775,7 +4830,7 @@
         <v>78</v>
       </c>
       <c r="AF25" t="s" s="2">
-        <v>229</v>
+        <v>237</v>
       </c>
       <c r="AG25" t="s" s="2">
         <v>79</v>
@@ -4784,30 +4839,30 @@
         <v>88</v>
       </c>
       <c r="AI25" t="s" s="2">
-        <v>78</v>
+        <v>150</v>
       </c>
       <c r="AJ25" t="s" s="2">
         <v>100</v>
       </c>
       <c r="AK25" t="s" s="2">
-        <v>233</v>
+        <v>241</v>
       </c>
       <c r="AL25" t="s" s="2">
-        <v>234</v>
+        <v>242</v>
       </c>
       <c r="AM25" t="s" s="2">
         <v>78</v>
       </c>
       <c r="AN25" t="s" s="2">
-        <v>78</v>
+        <v>207</v>
       </c>
     </row>
     <row r="26" hidden="true">
       <c r="A26" t="s" s="2">
-        <v>235</v>
+        <v>243</v>
       </c>
       <c r="B26" t="s" s="2">
-        <v>235</v>
+        <v>243</v>
       </c>
       <c r="C26" s="2"/>
       <c r="D26" t="s" s="2">
@@ -4830,19 +4885,19 @@
         <v>89</v>
       </c>
       <c r="K26" t="s" s="2">
-        <v>236</v>
+        <v>244</v>
       </c>
       <c r="L26" t="s" s="2">
-        <v>237</v>
+        <v>245</v>
       </c>
       <c r="M26" t="s" s="2">
-        <v>238</v>
+        <v>246</v>
       </c>
       <c r="N26" t="s" s="2">
-        <v>239</v>
+        <v>247</v>
       </c>
       <c r="O26" t="s" s="2">
-        <v>240</v>
+        <v>248</v>
       </c>
       <c r="P26" t="s" s="2">
         <v>78</v>
@@ -4891,7 +4946,7 @@
         <v>78</v>
       </c>
       <c r="AF26" t="s" s="2">
-        <v>235</v>
+        <v>243</v>
       </c>
       <c r="AG26" t="s" s="2">
         <v>79</v>
@@ -4900,16 +4955,16 @@
         <v>80</v>
       </c>
       <c r="AI26" t="s" s="2">
-        <v>78</v>
+        <v>150</v>
       </c>
       <c r="AJ26" t="s" s="2">
-        <v>100</v>
+        <v>234</v>
       </c>
       <c r="AK26" t="s" s="2">
-        <v>241</v>
+        <v>249</v>
       </c>
       <c r="AL26" t="s" s="2">
-        <v>242</v>
+        <v>250</v>
       </c>
       <c r="AM26" t="s" s="2">
         <v>78</v>
@@ -4920,10 +4975,10 @@
     </row>
     <row r="27">
       <c r="A27" t="s" s="2">
-        <v>243</v>
+        <v>251</v>
       </c>
       <c r="B27" t="s" s="2">
-        <v>243</v>
+        <v>251</v>
       </c>
       <c r="C27" s="2"/>
       <c r="D27" t="s" s="2">
@@ -4946,17 +5001,17 @@
         <v>89</v>
       </c>
       <c r="K27" t="s" s="2">
-        <v>164</v>
+        <v>167</v>
       </c>
       <c r="L27" t="s" s="2">
-        <v>244</v>
+        <v>252</v>
       </c>
       <c r="M27" t="s" s="2">
-        <v>245</v>
+        <v>253</v>
       </c>
       <c r="N27" s="2"/>
       <c r="O27" t="s" s="2">
-        <v>246</v>
+        <v>254</v>
       </c>
       <c r="P27" t="s" s="2">
         <v>78</v>
@@ -4981,11 +5036,11 @@
         <v>78</v>
       </c>
       <c r="X27" t="s" s="2">
-        <v>247</v>
+        <v>255</v>
       </c>
       <c r="Y27" s="2"/>
       <c r="Z27" t="s" s="2">
-        <v>248</v>
+        <v>256</v>
       </c>
       <c r="AA27" t="s" s="2">
         <v>78</v>
@@ -5003,7 +5058,7 @@
         <v>78</v>
       </c>
       <c r="AF27" t="s" s="2">
-        <v>243</v>
+        <v>251</v>
       </c>
       <c r="AG27" t="s" s="2">
         <v>88</v>
@@ -5018,13 +5073,13 @@
         <v>100</v>
       </c>
       <c r="AK27" t="s" s="2">
-        <v>249</v>
+        <v>257</v>
       </c>
       <c r="AL27" t="s" s="2">
-        <v>250</v>
+        <v>258</v>
       </c>
       <c r="AM27" t="s" s="2">
-        <v>251</v>
+        <v>259</v>
       </c>
       <c r="AN27" t="s" s="2">
         <v>78</v>
@@ -5032,10 +5087,10 @@
     </row>
     <row r="28" hidden="true">
       <c r="A28" t="s" s="2">
-        <v>252</v>
+        <v>260</v>
       </c>
       <c r="B28" t="s" s="2">
-        <v>252</v>
+        <v>260</v>
       </c>
       <c r="C28" s="2"/>
       <c r="D28" t="s" s="2">
@@ -5058,16 +5113,16 @@
         <v>89</v>
       </c>
       <c r="K28" t="s" s="2">
-        <v>253</v>
+        <v>261</v>
       </c>
       <c r="L28" t="s" s="2">
-        <v>254</v>
+        <v>262</v>
       </c>
       <c r="M28" t="s" s="2">
-        <v>255</v>
+        <v>263</v>
       </c>
       <c r="N28" t="s" s="2">
-        <v>256</v>
+        <v>264</v>
       </c>
       <c r="O28" s="2"/>
       <c r="P28" t="s" s="2">
@@ -5093,10 +5148,10 @@
         <v>78</v>
       </c>
       <c r="X28" t="s" s="2">
-        <v>154</v>
+        <v>157</v>
       </c>
       <c r="Y28" t="s" s="2">
-        <v>257</v>
+        <v>265</v>
       </c>
       <c r="Z28" t="s" s="2">
         <v>78</v>
@@ -5117,7 +5172,7 @@
         <v>78</v>
       </c>
       <c r="AF28" t="s" s="2">
-        <v>252</v>
+        <v>260</v>
       </c>
       <c r="AG28" t="s" s="2">
         <v>79</v>
@@ -5126,7 +5181,7 @@
         <v>88</v>
       </c>
       <c r="AI28" t="s" s="2">
-        <v>78</v>
+        <v>150</v>
       </c>
       <c r="AJ28" t="s" s="2">
         <v>100</v>
@@ -5135,21 +5190,21 @@
         <v>78</v>
       </c>
       <c r="AL28" t="s" s="2">
-        <v>258</v>
+        <v>266</v>
       </c>
       <c r="AM28" t="s" s="2">
         <v>78</v>
       </c>
       <c r="AN28" t="s" s="2">
-        <v>78</v>
+        <v>267</v>
       </c>
     </row>
     <row r="29" hidden="true">
       <c r="A29" t="s" s="2">
-        <v>259</v>
+        <v>268</v>
       </c>
       <c r="B29" t="s" s="2">
-        <v>259</v>
+        <v>268</v>
       </c>
       <c r="C29" s="2"/>
       <c r="D29" t="s" s="2">
@@ -5172,17 +5227,19 @@
         <v>89</v>
       </c>
       <c r="K29" t="s" s="2">
-        <v>253</v>
+        <v>261</v>
       </c>
       <c r="L29" t="s" s="2">
-        <v>260</v>
+        <v>269</v>
       </c>
       <c r="M29" t="s" s="2">
-        <v>261</v>
-      </c>
-      <c r="N29" s="2"/>
+        <v>270</v>
+      </c>
+      <c r="N29" t="s" s="2">
+        <v>271</v>
+      </c>
       <c r="O29" t="s" s="2">
-        <v>262</v>
+        <v>272</v>
       </c>
       <c r="P29" t="s" s="2">
         <v>78</v>
@@ -5207,10 +5264,10 @@
         <v>78</v>
       </c>
       <c r="X29" t="s" s="2">
-        <v>154</v>
+        <v>157</v>
       </c>
       <c r="Y29" t="s" s="2">
-        <v>263</v>
+        <v>273</v>
       </c>
       <c r="Z29" t="s" s="2">
         <v>78</v>
@@ -5231,7 +5288,7 @@
         <v>78</v>
       </c>
       <c r="AF29" t="s" s="2">
-        <v>259</v>
+        <v>268</v>
       </c>
       <c r="AG29" t="s" s="2">
         <v>79</v>
@@ -5240,7 +5297,7 @@
         <v>88</v>
       </c>
       <c r="AI29" t="s" s="2">
-        <v>78</v>
+        <v>150</v>
       </c>
       <c r="AJ29" t="s" s="2">
         <v>100</v>
@@ -5249,21 +5306,21 @@
         <v>78</v>
       </c>
       <c r="AL29" t="s" s="2">
-        <v>264</v>
+        <v>274</v>
       </c>
       <c r="AM29" t="s" s="2">
         <v>78</v>
       </c>
       <c r="AN29" t="s" s="2">
-        <v>78</v>
+        <v>267</v>
       </c>
     </row>
     <row r="30" hidden="true">
       <c r="A30" t="s" s="2">
-        <v>265</v>
+        <v>275</v>
       </c>
       <c r="B30" t="s" s="2">
-        <v>265</v>
+        <v>275</v>
       </c>
       <c r="C30" s="2"/>
       <c r="D30" t="s" s="2">
@@ -5286,16 +5343,16 @@
         <v>89</v>
       </c>
       <c r="K30" t="s" s="2">
-        <v>164</v>
+        <v>167</v>
       </c>
       <c r="L30" t="s" s="2">
-        <v>266</v>
+        <v>276</v>
       </c>
       <c r="M30" t="s" s="2">
-        <v>267</v>
+        <v>277</v>
       </c>
       <c r="N30" t="s" s="2">
-        <v>268</v>
+        <v>278</v>
       </c>
       <c r="O30" s="2"/>
       <c r="P30" t="s" s="2">
@@ -5303,7 +5360,7 @@
       </c>
       <c r="Q30" s="2"/>
       <c r="R30" t="s" s="2">
-        <v>269</v>
+        <v>279</v>
       </c>
       <c r="S30" t="s" s="2">
         <v>78</v>
@@ -5321,13 +5378,13 @@
         <v>78</v>
       </c>
       <c r="X30" t="s" s="2">
-        <v>247</v>
+        <v>255</v>
       </c>
       <c r="Y30" t="s" s="2">
-        <v>270</v>
+        <v>280</v>
       </c>
       <c r="Z30" t="s" s="2">
-        <v>271</v>
+        <v>281</v>
       </c>
       <c r="AA30" t="s" s="2">
         <v>78</v>
@@ -5345,7 +5402,7 @@
         <v>78</v>
       </c>
       <c r="AF30" t="s" s="2">
-        <v>265</v>
+        <v>275</v>
       </c>
       <c r="AG30" t="s" s="2">
         <v>88</v>
@@ -5360,13 +5417,13 @@
         <v>100</v>
       </c>
       <c r="AK30" t="s" s="2">
-        <v>272</v>
+        <v>282</v>
       </c>
       <c r="AL30" t="s" s="2">
-        <v>273</v>
+        <v>283</v>
       </c>
       <c r="AM30" t="s" s="2">
-        <v>274</v>
+        <v>284</v>
       </c>
       <c r="AN30" t="s" s="2">
         <v>78</v>
@@ -5374,10 +5431,10 @@
     </row>
     <row r="31" hidden="true">
       <c r="A31" t="s" s="2">
-        <v>275</v>
+        <v>285</v>
       </c>
       <c r="B31" t="s" s="2">
-        <v>275</v>
+        <v>285</v>
       </c>
       <c r="C31" s="2"/>
       <c r="D31" t="s" s="2">
@@ -5400,23 +5457,23 @@
         <v>78</v>
       </c>
       <c r="K31" t="s" s="2">
-        <v>164</v>
+        <v>167</v>
       </c>
       <c r="L31" t="s" s="2">
-        <v>276</v>
+        <v>286</v>
       </c>
       <c r="M31" t="s" s="2">
-        <v>277</v>
+        <v>287</v>
       </c>
       <c r="N31" s="2"/>
       <c r="O31" t="s" s="2">
-        <v>278</v>
+        <v>288</v>
       </c>
       <c r="P31" t="s" s="2">
         <v>78</v>
       </c>
       <c r="Q31" t="s" s="2">
-        <v>279</v>
+        <v>289</v>
       </c>
       <c r="R31" t="s" s="2">
         <v>78</v>
@@ -5437,13 +5494,13 @@
         <v>78</v>
       </c>
       <c r="X31" t="s" s="2">
-        <v>247</v>
+        <v>255</v>
       </c>
       <c r="Y31" t="s" s="2">
-        <v>280</v>
+        <v>290</v>
       </c>
       <c r="Z31" t="s" s="2">
-        <v>281</v>
+        <v>291</v>
       </c>
       <c r="AA31" t="s" s="2">
         <v>78</v>
@@ -5461,7 +5518,7 @@
         <v>78</v>
       </c>
       <c r="AF31" t="s" s="2">
-        <v>275</v>
+        <v>285</v>
       </c>
       <c r="AG31" t="s" s="2">
         <v>79</v>
@@ -5476,13 +5533,13 @@
         <v>100</v>
       </c>
       <c r="AK31" t="s" s="2">
-        <v>282</v>
+        <v>292</v>
       </c>
       <c r="AL31" t="s" s="2">
-        <v>283</v>
+        <v>293</v>
       </c>
       <c r="AM31" t="s" s="2">
-        <v>284</v>
+        <v>294</v>
       </c>
       <c r="AN31" t="s" s="2">
         <v>78</v>
@@ -5490,10 +5547,10 @@
     </row>
     <row r="32" hidden="true">
       <c r="A32" t="s" s="2">
-        <v>285</v>
+        <v>295</v>
       </c>
       <c r="B32" t="s" s="2">
-        <v>285</v>
+        <v>295</v>
       </c>
       <c r="C32" s="2"/>
       <c r="D32" t="s" s="2">
@@ -5516,16 +5573,16 @@
         <v>89</v>
       </c>
       <c r="K32" t="s" s="2">
-        <v>253</v>
+        <v>261</v>
       </c>
       <c r="L32" t="s" s="2">
-        <v>286</v>
+        <v>296</v>
       </c>
       <c r="M32" t="s" s="2">
-        <v>287</v>
+        <v>297</v>
       </c>
       <c r="N32" t="s" s="2">
-        <v>288</v>
+        <v>298</v>
       </c>
       <c r="O32" s="2"/>
       <c r="P32" t="s" s="2">
@@ -5551,13 +5608,13 @@
         <v>78</v>
       </c>
       <c r="X32" t="s" s="2">
-        <v>154</v>
+        <v>157</v>
       </c>
       <c r="Y32" t="s" s="2">
-        <v>289</v>
+        <v>299</v>
       </c>
       <c r="Z32" t="s" s="2">
-        <v>290</v>
+        <v>300</v>
       </c>
       <c r="AA32" t="s" s="2">
         <v>78</v>
@@ -5575,7 +5632,7 @@
         <v>78</v>
       </c>
       <c r="AF32" t="s" s="2">
-        <v>285</v>
+        <v>295</v>
       </c>
       <c r="AG32" t="s" s="2">
         <v>79</v>
@@ -5584,30 +5641,30 @@
         <v>88</v>
       </c>
       <c r="AI32" t="s" s="2">
-        <v>78</v>
+        <v>150</v>
       </c>
       <c r="AJ32" t="s" s="2">
         <v>100</v>
       </c>
       <c r="AK32" t="s" s="2">
-        <v>291</v>
+        <v>301</v>
       </c>
       <c r="AL32" t="s" s="2">
-        <v>292</v>
+        <v>302</v>
       </c>
       <c r="AM32" t="s" s="2">
-        <v>293</v>
+        <v>303</v>
       </c>
       <c r="AN32" t="s" s="2">
-        <v>78</v>
+        <v>267</v>
       </c>
     </row>
     <row r="33" hidden="true">
       <c r="A33" t="s" s="2">
-        <v>294</v>
+        <v>304</v>
       </c>
       <c r="B33" t="s" s="2">
-        <v>294</v>
+        <v>304</v>
       </c>
       <c r="C33" s="2"/>
       <c r="D33" t="s" s="2">
@@ -5633,12 +5690,14 @@
         <v>102</v>
       </c>
       <c r="L33" t="s" s="2">
-        <v>295</v>
+        <v>305</v>
       </c>
       <c r="M33" t="s" s="2">
-        <v>296</v>
-      </c>
-      <c r="N33" s="2"/>
+        <v>306</v>
+      </c>
+      <c r="N33" t="s" s="2">
+        <v>307</v>
+      </c>
       <c r="O33" s="2"/>
       <c r="P33" t="s" s="2">
         <v>78</v>
@@ -5687,7 +5746,7 @@
         <v>78</v>
       </c>
       <c r="AF33" t="s" s="2">
-        <v>294</v>
+        <v>304</v>
       </c>
       <c r="AG33" t="s" s="2">
         <v>79</v>
@@ -5705,7 +5764,7 @@
         <v>78</v>
       </c>
       <c r="AL33" t="s" s="2">
-        <v>297</v>
+        <v>308</v>
       </c>
       <c r="AM33" t="s" s="2">
         <v>78</v>
@@ -5716,10 +5775,10 @@
     </row>
     <row r="34" hidden="true">
       <c r="A34" t="s" s="2">
-        <v>298</v>
+        <v>309</v>
       </c>
       <c r="B34" t="s" s="2">
-        <v>298</v>
+        <v>309</v>
       </c>
       <c r="C34" s="2"/>
       <c r="D34" t="s" s="2">
@@ -5742,19 +5801,19 @@
         <v>89</v>
       </c>
       <c r="K34" t="s" s="2">
-        <v>224</v>
+        <v>230</v>
       </c>
       <c r="L34" t="s" s="2">
-        <v>299</v>
+        <v>310</v>
       </c>
       <c r="M34" t="s" s="2">
-        <v>300</v>
+        <v>311</v>
       </c>
       <c r="N34" t="s" s="2">
-        <v>301</v>
+        <v>312</v>
       </c>
       <c r="O34" t="s" s="2">
-        <v>302</v>
+        <v>313</v>
       </c>
       <c r="P34" t="s" s="2">
         <v>78</v>
@@ -5803,7 +5862,7 @@
         <v>78</v>
       </c>
       <c r="AF34" t="s" s="2">
-        <v>298</v>
+        <v>309</v>
       </c>
       <c r="AG34" t="s" s="2">
         <v>79</v>
@@ -5812,19 +5871,19 @@
         <v>88</v>
       </c>
       <c r="AI34" t="s" s="2">
-        <v>78</v>
+        <v>150</v>
       </c>
       <c r="AJ34" t="s" s="2">
-        <v>100</v>
+        <v>234</v>
       </c>
       <c r="AK34" t="s" s="2">
         <v>78</v>
       </c>
       <c r="AL34" t="s" s="2">
+        <v>314</v>
+      </c>
+      <c r="AM34" t="s" s="2">
         <v>303</v>
-      </c>
-      <c r="AM34" t="s" s="2">
-        <v>293</v>
       </c>
       <c r="AN34" t="s" s="2">
         <v>78</v>
@@ -5832,14 +5891,14 @@
     </row>
     <row r="35">
       <c r="A35" t="s" s="2">
-        <v>304</v>
+        <v>315</v>
       </c>
       <c r="B35" t="s" s="2">
-        <v>304</v>
+        <v>315</v>
       </c>
       <c r="C35" s="2"/>
       <c r="D35" t="s" s="2">
-        <v>305</v>
+        <v>316</v>
       </c>
       <c r="E35" s="2"/>
       <c r="F35" t="s" s="2">
@@ -5858,17 +5917,19 @@
         <v>89</v>
       </c>
       <c r="K35" t="s" s="2">
-        <v>224</v>
+        <v>230</v>
       </c>
       <c r="L35" t="s" s="2">
-        <v>306</v>
+        <v>317</v>
       </c>
       <c r="M35" t="s" s="2">
-        <v>307</v>
-      </c>
-      <c r="N35" s="2"/>
+        <v>318</v>
+      </c>
+      <c r="N35" t="s" s="2">
+        <v>233</v>
+      </c>
       <c r="O35" t="s" s="2">
-        <v>308</v>
+        <v>319</v>
       </c>
       <c r="P35" t="s" s="2">
         <v>78</v>
@@ -5917,7 +5978,7 @@
         <v>78</v>
       </c>
       <c r="AF35" t="s" s="2">
-        <v>304</v>
+        <v>315</v>
       </c>
       <c r="AG35" t="s" s="2">
         <v>79</v>
@@ -5926,19 +5987,19 @@
         <v>88</v>
       </c>
       <c r="AI35" t="s" s="2">
-        <v>78</v>
+        <v>150</v>
       </c>
       <c r="AJ35" t="s" s="2">
-        <v>100</v>
+        <v>234</v>
       </c>
       <c r="AK35" t="s" s="2">
-        <v>309</v>
+        <v>320</v>
       </c>
       <c r="AL35" t="s" s="2">
-        <v>310</v>
+        <v>321</v>
       </c>
       <c r="AM35" t="s" s="2">
-        <v>311</v>
+        <v>322</v>
       </c>
       <c r="AN35" t="s" s="2">
         <v>78</v>
@@ -5946,10 +6007,10 @@
     </row>
     <row r="36" hidden="true">
       <c r="A36" t="s" s="2">
-        <v>312</v>
+        <v>323</v>
       </c>
       <c r="B36" t="s" s="2">
-        <v>312</v>
+        <v>323</v>
       </c>
       <c r="C36" s="2"/>
       <c r="D36" t="s" s="2">
@@ -6058,10 +6119,10 @@
     </row>
     <row r="37" hidden="true">
       <c r="A37" t="s" s="2">
-        <v>313</v>
+        <v>324</v>
       </c>
       <c r="B37" t="s" s="2">
-        <v>313</v>
+        <v>324</v>
       </c>
       <c r="C37" s="2"/>
       <c r="D37" t="s" s="2">
@@ -6172,10 +6233,10 @@
     </row>
     <row r="38" hidden="true">
       <c r="A38" t="s" s="2">
-        <v>314</v>
+        <v>325</v>
       </c>
       <c r="B38" t="s" s="2">
-        <v>314</v>
+        <v>325</v>
       </c>
       <c r="C38" s="2"/>
       <c r="D38" t="s" s="2">
@@ -6201,13 +6262,13 @@
         <v>102</v>
       </c>
       <c r="L38" t="s" s="2">
-        <v>315</v>
+        <v>326</v>
       </c>
       <c r="M38" t="s" s="2">
-        <v>316</v>
+        <v>327</v>
       </c>
       <c r="N38" t="s" s="2">
-        <v>317</v>
+        <v>328</v>
       </c>
       <c r="O38" s="2"/>
       <c r="P38" t="s" s="2">
@@ -6257,7 +6318,7 @@
         <v>78</v>
       </c>
       <c r="AF38" t="s" s="2">
-        <v>318</v>
+        <v>329</v>
       </c>
       <c r="AG38" t="s" s="2">
         <v>79</v>
@@ -6266,7 +6327,7 @@
         <v>88</v>
       </c>
       <c r="AI38" t="s" s="2">
-        <v>319</v>
+        <v>330</v>
       </c>
       <c r="AJ38" t="s" s="2">
         <v>100</v>
@@ -6275,7 +6336,7 @@
         <v>78</v>
       </c>
       <c r="AL38" t="s" s="2">
-        <v>187</v>
+        <v>190</v>
       </c>
       <c r="AM38" t="s" s="2">
         <v>78</v>
@@ -6286,10 +6347,10 @@
     </row>
     <row r="39" hidden="true">
       <c r="A39" t="s" s="2">
-        <v>320</v>
+        <v>331</v>
       </c>
       <c r="B39" t="s" s="2">
-        <v>320</v>
+        <v>331</v>
       </c>
       <c r="C39" s="2"/>
       <c r="D39" t="s" s="2">
@@ -6315,13 +6376,13 @@
         <v>130</v>
       </c>
       <c r="L39" t="s" s="2">
-        <v>321</v>
+        <v>332</v>
       </c>
       <c r="M39" t="s" s="2">
-        <v>322</v>
+        <v>333</v>
       </c>
       <c r="N39" t="s" s="2">
-        <v>323</v>
+        <v>334</v>
       </c>
       <c r="O39" s="2"/>
       <c r="P39" t="s" s="2">
@@ -6350,10 +6411,10 @@
         <v>146</v>
       </c>
       <c r="Y39" t="s" s="2">
-        <v>324</v>
+        <v>335</v>
       </c>
       <c r="Z39" t="s" s="2">
-        <v>325</v>
+        <v>336</v>
       </c>
       <c r="AA39" t="s" s="2">
         <v>78</v>
@@ -6371,7 +6432,7 @@
         <v>78</v>
       </c>
       <c r="AF39" t="s" s="2">
-        <v>326</v>
+        <v>337</v>
       </c>
       <c r="AG39" t="s" s="2">
         <v>79</v>
@@ -6389,7 +6450,7 @@
         <v>78</v>
       </c>
       <c r="AL39" t="s" s="2">
-        <v>187</v>
+        <v>190</v>
       </c>
       <c r="AM39" t="s" s="2">
         <v>78</v>
@@ -6400,10 +6461,10 @@
     </row>
     <row r="40">
       <c r="A40" t="s" s="2">
-        <v>327</v>
+        <v>338</v>
       </c>
       <c r="B40" t="s" s="2">
-        <v>327</v>
+        <v>338</v>
       </c>
       <c r="C40" s="2"/>
       <c r="D40" t="s" s="2">
@@ -6426,16 +6487,16 @@
         <v>89</v>
       </c>
       <c r="K40" t="s" s="2">
-        <v>328</v>
+        <v>339</v>
       </c>
       <c r="L40" t="s" s="2">
-        <v>329</v>
+        <v>340</v>
       </c>
       <c r="M40" t="s" s="2">
-        <v>330</v>
+        <v>341</v>
       </c>
       <c r="N40" t="s" s="2">
-        <v>331</v>
+        <v>342</v>
       </c>
       <c r="O40" s="2"/>
       <c r="P40" t="s" s="2">
@@ -6485,7 +6546,7 @@
         <v>78</v>
       </c>
       <c r="AF40" t="s" s="2">
-        <v>332</v>
+        <v>343</v>
       </c>
       <c r="AG40" t="s" s="2">
         <v>79</v>
@@ -6494,7 +6555,7 @@
         <v>88</v>
       </c>
       <c r="AI40" t="s" s="2">
-        <v>78</v>
+        <v>150</v>
       </c>
       <c r="AJ40" t="s" s="2">
         <v>100</v>
@@ -6503,21 +6564,21 @@
         <v>78</v>
       </c>
       <c r="AL40" t="s" s="2">
-        <v>333</v>
+        <v>344</v>
       </c>
       <c r="AM40" t="s" s="2">
         <v>78</v>
       </c>
       <c r="AN40" t="s" s="2">
-        <v>78</v>
+        <v>207</v>
       </c>
     </row>
     <row r="41" hidden="true">
       <c r="A41" t="s" s="2">
-        <v>334</v>
+        <v>345</v>
       </c>
       <c r="B41" t="s" s="2">
-        <v>334</v>
+        <v>345</v>
       </c>
       <c r="C41" s="2"/>
       <c r="D41" t="s" s="2">
@@ -6543,13 +6604,13 @@
         <v>102</v>
       </c>
       <c r="L41" t="s" s="2">
-        <v>335</v>
+        <v>346</v>
       </c>
       <c r="M41" t="s" s="2">
-        <v>336</v>
+        <v>347</v>
       </c>
       <c r="N41" t="s" s="2">
-        <v>337</v>
+        <v>348</v>
       </c>
       <c r="O41" s="2"/>
       <c r="P41" t="s" s="2">
@@ -6599,7 +6660,7 @@
         <v>78</v>
       </c>
       <c r="AF41" t="s" s="2">
-        <v>338</v>
+        <v>349</v>
       </c>
       <c r="AG41" t="s" s="2">
         <v>79</v>
@@ -6617,7 +6678,7 @@
         <v>78</v>
       </c>
       <c r="AL41" t="s" s="2">
-        <v>187</v>
+        <v>190</v>
       </c>
       <c r="AM41" t="s" s="2">
         <v>78</v>
@@ -6628,10 +6689,10 @@
     </row>
     <row r="42" hidden="true">
       <c r="A42" t="s" s="2">
-        <v>339</v>
+        <v>350</v>
       </c>
       <c r="B42" t="s" s="2">
-        <v>339</v>
+        <v>350</v>
       </c>
       <c r="C42" s="2"/>
       <c r="D42" t="s" s="2">
@@ -6654,17 +6715,19 @@
         <v>89</v>
       </c>
       <c r="K42" t="s" s="2">
-        <v>340</v>
+        <v>351</v>
       </c>
       <c r="L42" t="s" s="2">
-        <v>341</v>
+        <v>352</v>
       </c>
       <c r="M42" t="s" s="2">
-        <v>342</v>
-      </c>
-      <c r="N42" s="2"/>
+        <v>353</v>
+      </c>
+      <c r="N42" t="s" s="2">
+        <v>233</v>
+      </c>
       <c r="O42" t="s" s="2">
-        <v>343</v>
+        <v>354</v>
       </c>
       <c r="P42" t="s" s="2">
         <v>78</v>
@@ -6713,7 +6776,7 @@
         <v>78</v>
       </c>
       <c r="AF42" t="s" s="2">
-        <v>339</v>
+        <v>350</v>
       </c>
       <c r="AG42" t="s" s="2">
         <v>79</v>
@@ -6722,19 +6785,19 @@
         <v>88</v>
       </c>
       <c r="AI42" t="s" s="2">
-        <v>78</v>
+        <v>150</v>
       </c>
       <c r="AJ42" t="s" s="2">
-        <v>100</v>
+        <v>234</v>
       </c>
       <c r="AK42" t="s" s="2">
-        <v>344</v>
+        <v>355</v>
       </c>
       <c r="AL42" t="s" s="2">
-        <v>345</v>
+        <v>356</v>
       </c>
       <c r="AM42" t="s" s="2">
-        <v>346</v>
+        <v>357</v>
       </c>
       <c r="AN42" t="s" s="2">
         <v>78</v>
@@ -6742,10 +6805,10 @@
     </row>
     <row r="43" hidden="true">
       <c r="A43" t="s" s="2">
-        <v>347</v>
+        <v>358</v>
       </c>
       <c r="B43" t="s" s="2">
-        <v>347</v>
+        <v>358</v>
       </c>
       <c r="C43" s="2"/>
       <c r="D43" t="s" s="2">
@@ -6768,15 +6831,17 @@
         <v>89</v>
       </c>
       <c r="K43" t="s" s="2">
-        <v>348</v>
+        <v>359</v>
       </c>
       <c r="L43" t="s" s="2">
-        <v>349</v>
+        <v>360</v>
       </c>
       <c r="M43" t="s" s="2">
-        <v>350</v>
-      </c>
-      <c r="N43" s="2"/>
+        <v>361</v>
+      </c>
+      <c r="N43" t="s" s="2">
+        <v>362</v>
+      </c>
       <c r="O43" s="2"/>
       <c r="P43" t="s" s="2">
         <v>78</v>
@@ -6825,7 +6890,7 @@
         <v>78</v>
       </c>
       <c r="AF43" t="s" s="2">
-        <v>347</v>
+        <v>358</v>
       </c>
       <c r="AG43" t="s" s="2">
         <v>79</v>
@@ -6834,34 +6899,34 @@
         <v>88</v>
       </c>
       <c r="AI43" t="s" s="2">
-        <v>78</v>
+        <v>150</v>
       </c>
       <c r="AJ43" t="s" s="2">
-        <v>100</v>
+        <v>363</v>
       </c>
       <c r="AK43" t="s" s="2">
-        <v>351</v>
+        <v>364</v>
       </c>
       <c r="AL43" t="s" s="2">
-        <v>352</v>
+        <v>365</v>
       </c>
       <c r="AM43" t="s" s="2">
-        <v>353</v>
+        <v>366</v>
       </c>
       <c r="AN43" t="s" s="2">
-        <v>78</v>
+        <v>367</v>
       </c>
     </row>
     <row r="44" hidden="true">
       <c r="A44" t="s" s="2">
-        <v>354</v>
+        <v>368</v>
       </c>
       <c r="B44" t="s" s="2">
-        <v>354</v>
+        <v>368</v>
       </c>
       <c r="C44" s="2"/>
       <c r="D44" t="s" s="2">
-        <v>355</v>
+        <v>369</v>
       </c>
       <c r="E44" s="2"/>
       <c r="F44" t="s" s="2">
@@ -6880,17 +6945,17 @@
         <v>78</v>
       </c>
       <c r="K44" t="s" s="2">
-        <v>356</v>
+        <v>370</v>
       </c>
       <c r="L44" t="s" s="2">
-        <v>357</v>
+        <v>371</v>
       </c>
       <c r="M44" t="s" s="2">
-        <v>358</v>
+        <v>372</v>
       </c>
       <c r="N44" s="2"/>
       <c r="O44" t="s" s="2">
-        <v>359</v>
+        <v>373</v>
       </c>
       <c r="P44" t="s" s="2">
         <v>78</v>
@@ -6939,7 +7004,7 @@
         <v>78</v>
       </c>
       <c r="AF44" t="s" s="2">
-        <v>354</v>
+        <v>368</v>
       </c>
       <c r="AG44" t="s" s="2">
         <v>79</v>
@@ -6948,19 +7013,19 @@
         <v>88</v>
       </c>
       <c r="AI44" t="s" s="2">
-        <v>360</v>
+        <v>374</v>
       </c>
       <c r="AJ44" t="s" s="2">
         <v>100</v>
       </c>
       <c r="AK44" t="s" s="2">
-        <v>361</v>
+        <v>375</v>
       </c>
       <c r="AL44" t="s" s="2">
-        <v>362</v>
+        <v>376</v>
       </c>
       <c r="AM44" t="s" s="2">
-        <v>363</v>
+        <v>377</v>
       </c>
       <c r="AN44" t="s" s="2">
         <v>78</v>
@@ -6968,14 +7033,14 @@
     </row>
     <row r="45" hidden="true">
       <c r="A45" t="s" s="2">
-        <v>364</v>
+        <v>378</v>
       </c>
       <c r="B45" t="s" s="2">
-        <v>364</v>
+        <v>378</v>
       </c>
       <c r="C45" s="2"/>
       <c r="D45" t="s" s="2">
-        <v>365</v>
+        <v>379</v>
       </c>
       <c r="E45" s="2"/>
       <c r="F45" t="s" s="2">
@@ -6994,17 +7059,17 @@
         <v>89</v>
       </c>
       <c r="K45" t="s" s="2">
-        <v>356</v>
+        <v>370</v>
       </c>
       <c r="L45" t="s" s="2">
-        <v>366</v>
+        <v>380</v>
       </c>
       <c r="M45" t="s" s="2">
-        <v>367</v>
+        <v>381</v>
       </c>
       <c r="N45" s="2"/>
       <c r="O45" t="s" s="2">
-        <v>368</v>
+        <v>382</v>
       </c>
       <c r="P45" t="s" s="2">
         <v>78</v>
@@ -7053,7 +7118,7 @@
         <v>78</v>
       </c>
       <c r="AF45" t="s" s="2">
-        <v>364</v>
+        <v>378</v>
       </c>
       <c r="AG45" t="s" s="2">
         <v>79</v>
@@ -7062,7 +7127,7 @@
         <v>88</v>
       </c>
       <c r="AI45" t="s" s="2">
-        <v>360</v>
+        <v>374</v>
       </c>
       <c r="AJ45" t="s" s="2">
         <v>100</v>
@@ -7071,7 +7136,7 @@
         <v>78</v>
       </c>
       <c r="AL45" t="s" s="2">
-        <v>369</v>
+        <v>383</v>
       </c>
       <c r="AM45" t="s" s="2">
         <v>78</v>
@@ -7082,10 +7147,10 @@
     </row>
     <row r="46" hidden="true">
       <c r="A46" t="s" s="2">
-        <v>370</v>
+        <v>384</v>
       </c>
       <c r="B46" t="s" s="2">
-        <v>370</v>
+        <v>384</v>
       </c>
       <c r="C46" s="2"/>
       <c r="D46" t="s" s="2">
@@ -7108,17 +7173,19 @@
         <v>89</v>
       </c>
       <c r="K46" t="s" s="2">
-        <v>371</v>
+        <v>385</v>
       </c>
       <c r="L46" t="s" s="2">
-        <v>372</v>
+        <v>386</v>
       </c>
       <c r="M46" t="s" s="2">
-        <v>373</v>
-      </c>
-      <c r="N46" s="2"/>
+        <v>387</v>
+      </c>
+      <c r="N46" t="s" s="2">
+        <v>233</v>
+      </c>
       <c r="O46" t="s" s="2">
-        <v>374</v>
+        <v>388</v>
       </c>
       <c r="P46" t="s" s="2">
         <v>78</v>
@@ -7167,7 +7234,7 @@
         <v>78</v>
       </c>
       <c r="AF46" t="s" s="2">
-        <v>370</v>
+        <v>384</v>
       </c>
       <c r="AG46" t="s" s="2">
         <v>79</v>
@@ -7176,19 +7243,19 @@
         <v>88</v>
       </c>
       <c r="AI46" t="s" s="2">
-        <v>78</v>
+        <v>150</v>
       </c>
       <c r="AJ46" t="s" s="2">
-        <v>100</v>
+        <v>234</v>
       </c>
       <c r="AK46" t="s" s="2">
-        <v>375</v>
+        <v>389</v>
       </c>
       <c r="AL46" t="s" s="2">
-        <v>376</v>
+        <v>390</v>
       </c>
       <c r="AM46" t="s" s="2">
-        <v>377</v>
+        <v>391</v>
       </c>
       <c r="AN46" t="s" s="2">
         <v>78</v>
@@ -7196,10 +7263,10 @@
     </row>
     <row r="47" hidden="true">
       <c r="A47" t="s" s="2">
-        <v>378</v>
+        <v>392</v>
       </c>
       <c r="B47" t="s" s="2">
-        <v>378</v>
+        <v>392</v>
       </c>
       <c r="C47" s="2"/>
       <c r="D47" t="s" s="2">
@@ -7222,17 +7289,19 @@
         <v>78</v>
       </c>
       <c r="K47" t="s" s="2">
-        <v>253</v>
+        <v>261</v>
       </c>
       <c r="L47" t="s" s="2">
-        <v>379</v>
+        <v>393</v>
       </c>
       <c r="M47" t="s" s="2">
-        <v>380</v>
-      </c>
-      <c r="N47" s="2"/>
+        <v>394</v>
+      </c>
+      <c r="N47" t="s" s="2">
+        <v>271</v>
+      </c>
       <c r="O47" t="s" s="2">
-        <v>381</v>
+        <v>395</v>
       </c>
       <c r="P47" t="s" s="2">
         <v>78</v>
@@ -7257,13 +7326,13 @@
         <v>78</v>
       </c>
       <c r="X47" t="s" s="2">
-        <v>168</v>
+        <v>171</v>
       </c>
       <c r="Y47" t="s" s="2">
-        <v>382</v>
+        <v>396</v>
       </c>
       <c r="Z47" t="s" s="2">
-        <v>383</v>
+        <v>397</v>
       </c>
       <c r="AA47" t="s" s="2">
         <v>78</v>
@@ -7281,7 +7350,7 @@
         <v>78</v>
       </c>
       <c r="AF47" t="s" s="2">
-        <v>378</v>
+        <v>392</v>
       </c>
       <c r="AG47" t="s" s="2">
         <v>79</v>
@@ -7290,34 +7359,34 @@
         <v>80</v>
       </c>
       <c r="AI47" t="s" s="2">
-        <v>78</v>
+        <v>150</v>
       </c>
       <c r="AJ47" t="s" s="2">
         <v>100</v>
       </c>
       <c r="AK47" t="s" s="2">
-        <v>384</v>
+        <v>398</v>
       </c>
       <c r="AL47" t="s" s="2">
-        <v>385</v>
+        <v>399</v>
       </c>
       <c r="AM47" t="s" s="2">
-        <v>386</v>
+        <v>400</v>
       </c>
       <c r="AN47" t="s" s="2">
-        <v>78</v>
+        <v>267</v>
       </c>
     </row>
     <row r="48" hidden="true">
       <c r="A48" t="s" s="2">
-        <v>387</v>
+        <v>401</v>
       </c>
       <c r="B48" t="s" s="2">
-        <v>387</v>
+        <v>401</v>
       </c>
       <c r="C48" s="2"/>
       <c r="D48" t="s" s="2">
-        <v>388</v>
+        <v>402</v>
       </c>
       <c r="E48" s="2"/>
       <c r="F48" t="s" s="2">
@@ -7336,19 +7405,19 @@
         <v>89</v>
       </c>
       <c r="K48" t="s" s="2">
-        <v>389</v>
+        <v>403</v>
       </c>
       <c r="L48" t="s" s="2">
-        <v>390</v>
+        <v>404</v>
       </c>
       <c r="M48" t="s" s="2">
-        <v>391</v>
+        <v>405</v>
       </c>
       <c r="N48" t="s" s="2">
-        <v>392</v>
+        <v>406</v>
       </c>
       <c r="O48" t="s" s="2">
-        <v>393</v>
+        <v>407</v>
       </c>
       <c r="P48" t="s" s="2">
         <v>78</v>
@@ -7397,7 +7466,7 @@
         <v>78</v>
       </c>
       <c r="AF48" t="s" s="2">
-        <v>387</v>
+        <v>401</v>
       </c>
       <c r="AG48" t="s" s="2">
         <v>79</v>
@@ -7406,19 +7475,19 @@
         <v>88</v>
       </c>
       <c r="AI48" t="s" s="2">
-        <v>78</v>
+        <v>150</v>
       </c>
       <c r="AJ48" t="s" s="2">
-        <v>100</v>
+        <v>234</v>
       </c>
       <c r="AK48" t="s" s="2">
-        <v>394</v>
+        <v>408</v>
       </c>
       <c r="AL48" t="s" s="2">
-        <v>395</v>
+        <v>409</v>
       </c>
       <c r="AM48" t="s" s="2">
-        <v>386</v>
+        <v>400</v>
       </c>
       <c r="AN48" t="s" s="2">
         <v>78</v>
@@ -7426,10 +7495,10 @@
     </row>
     <row r="49" hidden="true">
       <c r="A49" t="s" s="2">
-        <v>396</v>
+        <v>410</v>
       </c>
       <c r="B49" t="s" s="2">
-        <v>396</v>
+        <v>410</v>
       </c>
       <c r="C49" s="2"/>
       <c r="D49" t="s" s="2">
@@ -7452,17 +7521,19 @@
         <v>89</v>
       </c>
       <c r="K49" t="s" s="2">
-        <v>397</v>
+        <v>411</v>
       </c>
       <c r="L49" t="s" s="2">
-        <v>398</v>
+        <v>412</v>
       </c>
       <c r="M49" t="s" s="2">
-        <v>399</v>
-      </c>
-      <c r="N49" s="2"/>
+        <v>413</v>
+      </c>
+      <c r="N49" t="s" s="2">
+        <v>233</v>
+      </c>
       <c r="O49" t="s" s="2">
-        <v>400</v>
+        <v>414</v>
       </c>
       <c r="P49" t="s" s="2">
         <v>78</v>
@@ -7511,7 +7582,7 @@
         <v>78</v>
       </c>
       <c r="AF49" t="s" s="2">
-        <v>396</v>
+        <v>410</v>
       </c>
       <c r="AG49" t="s" s="2">
         <v>79</v>
@@ -7520,19 +7591,19 @@
         <v>88</v>
       </c>
       <c r="AI49" t="s" s="2">
-        <v>78</v>
+        <v>150</v>
       </c>
       <c r="AJ49" t="s" s="2">
-        <v>100</v>
+        <v>234</v>
       </c>
       <c r="AK49" t="s" s="2">
-        <v>401</v>
+        <v>415</v>
       </c>
       <c r="AL49" t="s" s="2">
-        <v>402</v>
+        <v>416</v>
       </c>
       <c r="AM49" t="s" s="2">
-        <v>403</v>
+        <v>417</v>
       </c>
       <c r="AN49" t="s" s="2">
         <v>78</v>
@@ -7540,10 +7611,10 @@
     </row>
     <row r="50" hidden="true">
       <c r="A50" t="s" s="2">
-        <v>404</v>
+        <v>418</v>
       </c>
       <c r="B50" t="s" s="2">
-        <v>404</v>
+        <v>418</v>
       </c>
       <c r="C50" s="2"/>
       <c r="D50" t="s" s="2">
@@ -7566,16 +7637,16 @@
         <v>78</v>
       </c>
       <c r="K50" t="s" s="2">
-        <v>253</v>
+        <v>261</v>
       </c>
       <c r="L50" t="s" s="2">
-        <v>405</v>
+        <v>419</v>
       </c>
       <c r="M50" t="s" s="2">
-        <v>406</v>
+        <v>420</v>
       </c>
       <c r="N50" t="s" s="2">
-        <v>407</v>
+        <v>421</v>
       </c>
       <c r="O50" s="2"/>
       <c r="P50" t="s" s="2">
@@ -7601,10 +7672,10 @@
         <v>78</v>
       </c>
       <c r="X50" t="s" s="2">
-        <v>154</v>
+        <v>157</v>
       </c>
       <c r="Y50" t="s" s="2">
-        <v>408</v>
+        <v>422</v>
       </c>
       <c r="Z50" t="s" s="2">
         <v>78</v>
@@ -7625,7 +7696,7 @@
         <v>78</v>
       </c>
       <c r="AF50" t="s" s="2">
-        <v>404</v>
+        <v>418</v>
       </c>
       <c r="AG50" t="s" s="2">
         <v>79</v>
@@ -7634,30 +7705,30 @@
         <v>88</v>
       </c>
       <c r="AI50" t="s" s="2">
-        <v>78</v>
+        <v>150</v>
       </c>
       <c r="AJ50" t="s" s="2">
         <v>100</v>
       </c>
       <c r="AK50" t="s" s="2">
-        <v>409</v>
+        <v>423</v>
       </c>
       <c r="AL50" t="s" s="2">
-        <v>410</v>
+        <v>424</v>
       </c>
       <c r="AM50" t="s" s="2">
-        <v>411</v>
+        <v>425</v>
       </c>
       <c r="AN50" t="s" s="2">
-        <v>412</v>
+        <v>426</v>
       </c>
     </row>
     <row r="51" hidden="true">
       <c r="A51" t="s" s="2">
-        <v>413</v>
+        <v>427</v>
       </c>
       <c r="B51" t="s" s="2">
-        <v>413</v>
+        <v>427</v>
       </c>
       <c r="C51" s="2"/>
       <c r="D51" t="s" s="2">
@@ -7680,16 +7751,16 @@
         <v>78</v>
       </c>
       <c r="K51" t="s" s="2">
-        <v>224</v>
+        <v>230</v>
       </c>
       <c r="L51" t="s" s="2">
-        <v>405</v>
+        <v>419</v>
       </c>
       <c r="M51" t="s" s="2">
-        <v>414</v>
+        <v>428</v>
       </c>
       <c r="N51" t="s" s="2">
-        <v>415</v>
+        <v>429</v>
       </c>
       <c r="O51" s="2"/>
       <c r="P51" t="s" s="2">
@@ -7739,7 +7810,7 @@
         <v>78</v>
       </c>
       <c r="AF51" t="s" s="2">
-        <v>413</v>
+        <v>427</v>
       </c>
       <c r="AG51" t="s" s="2">
         <v>79</v>
@@ -7748,19 +7819,19 @@
         <v>88</v>
       </c>
       <c r="AI51" t="s" s="2">
-        <v>78</v>
+        <v>150</v>
       </c>
       <c r="AJ51" t="s" s="2">
-        <v>100</v>
+        <v>234</v>
       </c>
       <c r="AK51" t="s" s="2">
-        <v>416</v>
+        <v>430</v>
       </c>
       <c r="AL51" t="s" s="2">
-        <v>417</v>
+        <v>431</v>
       </c>
       <c r="AM51" t="s" s="2">
-        <v>411</v>
+        <v>425</v>
       </c>
       <c r="AN51" t="s" s="2">
         <v>78</v>
@@ -7768,10 +7839,10 @@
     </row>
     <row r="52" hidden="true">
       <c r="A52" t="s" s="2">
-        <v>418</v>
+        <v>432</v>
       </c>
       <c r="B52" t="s" s="2">
-        <v>418</v>
+        <v>432</v>
       </c>
       <c r="C52" s="2"/>
       <c r="D52" t="s" s="2">
@@ -7794,15 +7865,17 @@
         <v>78</v>
       </c>
       <c r="K52" t="s" s="2">
-        <v>419</v>
+        <v>433</v>
       </c>
       <c r="L52" t="s" s="2">
-        <v>420</v>
+        <v>434</v>
       </c>
       <c r="M52" t="s" s="2">
-        <v>421</v>
-      </c>
-      <c r="N52" s="2"/>
+        <v>435</v>
+      </c>
+      <c r="N52" t="s" s="2">
+        <v>233</v>
+      </c>
       <c r="O52" s="2"/>
       <c r="P52" t="s" s="2">
         <v>78</v>
@@ -7851,7 +7924,7 @@
         <v>78</v>
       </c>
       <c r="AF52" t="s" s="2">
-        <v>418</v>
+        <v>432</v>
       </c>
       <c r="AG52" t="s" s="2">
         <v>79</v>
@@ -7860,30 +7933,30 @@
         <v>80</v>
       </c>
       <c r="AI52" t="s" s="2">
-        <v>78</v>
+        <v>150</v>
       </c>
       <c r="AJ52" t="s" s="2">
-        <v>100</v>
+        <v>234</v>
       </c>
       <c r="AK52" t="s" s="2">
-        <v>422</v>
+        <v>436</v>
       </c>
       <c r="AL52" t="s" s="2">
-        <v>423</v>
+        <v>437</v>
       </c>
       <c r="AM52" t="s" s="2">
         <v>78</v>
       </c>
       <c r="AN52" t="s" s="2">
-        <v>424</v>
+        <v>438</v>
       </c>
     </row>
     <row r="53" hidden="true">
       <c r="A53" t="s" s="2">
-        <v>425</v>
+        <v>439</v>
       </c>
       <c r="B53" t="s" s="2">
-        <v>425</v>
+        <v>439</v>
       </c>
       <c r="C53" s="2"/>
       <c r="D53" t="s" s="2">
@@ -7906,15 +7979,17 @@
         <v>78</v>
       </c>
       <c r="K53" t="s" s="2">
-        <v>426</v>
+        <v>440</v>
       </c>
       <c r="L53" t="s" s="2">
-        <v>427</v>
+        <v>441</v>
       </c>
       <c r="M53" t="s" s="2">
-        <v>428</v>
-      </c>
-      <c r="N53" s="2"/>
+        <v>442</v>
+      </c>
+      <c r="N53" t="s" s="2">
+        <v>443</v>
+      </c>
       <c r="O53" s="2"/>
       <c r="P53" t="s" s="2">
         <v>78</v>
@@ -7963,7 +8038,7 @@
         <v>78</v>
       </c>
       <c r="AF53" t="s" s="2">
-        <v>425</v>
+        <v>439</v>
       </c>
       <c r="AG53" t="s" s="2">
         <v>79</v>
@@ -7972,34 +8047,34 @@
         <v>80</v>
       </c>
       <c r="AI53" t="s" s="2">
-        <v>78</v>
+        <v>150</v>
       </c>
       <c r="AJ53" t="s" s="2">
         <v>100</v>
       </c>
       <c r="AK53" t="s" s="2">
-        <v>429</v>
+        <v>444</v>
       </c>
       <c r="AL53" t="s" s="2">
-        <v>430</v>
+        <v>445</v>
       </c>
       <c r="AM53" t="s" s="2">
         <v>78</v>
       </c>
       <c r="AN53" t="s" s="2">
-        <v>78</v>
+        <v>190</v>
       </c>
     </row>
     <row r="54" hidden="true">
       <c r="A54" t="s" s="2">
-        <v>431</v>
+        <v>446</v>
       </c>
       <c r="B54" t="s" s="2">
-        <v>431</v>
+        <v>446</v>
       </c>
       <c r="C54" s="2"/>
       <c r="D54" t="s" s="2">
-        <v>432</v>
+        <v>447</v>
       </c>
       <c r="E54" s="2"/>
       <c r="F54" t="s" s="2">
@@ -8018,16 +8093,16 @@
         <v>78</v>
       </c>
       <c r="K54" t="s" s="2">
-        <v>433</v>
+        <v>448</v>
       </c>
       <c r="L54" t="s" s="2">
-        <v>434</v>
+        <v>449</v>
       </c>
       <c r="M54" t="s" s="2">
-        <v>435</v>
+        <v>450</v>
       </c>
       <c r="N54" t="s" s="2">
-        <v>436</v>
+        <v>451</v>
       </c>
       <c r="O54" s="2"/>
       <c r="P54" t="s" s="2">
@@ -8077,7 +8152,7 @@
         <v>78</v>
       </c>
       <c r="AF54" t="s" s="2">
-        <v>431</v>
+        <v>446</v>
       </c>
       <c r="AG54" t="s" s="2">
         <v>79</v>
@@ -8086,16 +8161,16 @@
         <v>80</v>
       </c>
       <c r="AI54" t="s" s="2">
-        <v>78</v>
+        <v>150</v>
       </c>
       <c r="AJ54" t="s" s="2">
-        <v>100</v>
+        <v>234</v>
       </c>
       <c r="AK54" t="s" s="2">
-        <v>437</v>
+        <v>452</v>
       </c>
       <c r="AL54" t="s" s="2">
-        <v>438</v>
+        <v>453</v>
       </c>
       <c r="AM54" t="s" s="2">
         <v>78</v>
@@ -8106,10 +8181,10 @@
     </row>
     <row r="55" hidden="true">
       <c r="A55" t="s" s="2">
-        <v>439</v>
+        <v>454</v>
       </c>
       <c r="B55" t="s" s="2">
-        <v>439</v>
+        <v>454</v>
       </c>
       <c r="C55" s="2"/>
       <c r="D55" t="s" s="2">
@@ -8132,17 +8207,17 @@
         <v>78</v>
       </c>
       <c r="K55" t="s" s="2">
-        <v>440</v>
+        <v>455</v>
       </c>
       <c r="L55" t="s" s="2">
-        <v>441</v>
+        <v>456</v>
       </c>
       <c r="M55" t="s" s="2">
-        <v>442</v>
+        <v>457</v>
       </c>
       <c r="N55" s="2"/>
       <c r="O55" t="s" s="2">
-        <v>443</v>
+        <v>458</v>
       </c>
       <c r="P55" t="s" s="2">
         <v>78</v>
@@ -8191,7 +8266,7 @@
         <v>78</v>
       </c>
       <c r="AF55" t="s" s="2">
-        <v>439</v>
+        <v>454</v>
       </c>
       <c r="AG55" t="s" s="2">
         <v>79</v>
@@ -8200,7 +8275,7 @@
         <v>88</v>
       </c>
       <c r="AI55" t="s" s="2">
-        <v>78</v>
+        <v>150</v>
       </c>
       <c r="AJ55" t="s" s="2">
         <v>100</v>
@@ -8209,7 +8284,7 @@
         <v>78</v>
       </c>
       <c r="AL55" t="s" s="2">
-        <v>444</v>
+        <v>459</v>
       </c>
       <c r="AM55" t="s" s="2">
         <v>78</v>
@@ -8220,10 +8295,10 @@
     </row>
     <row r="56" hidden="true">
       <c r="A56" t="s" s="2">
-        <v>445</v>
+        <v>460</v>
       </c>
       <c r="B56" t="s" s="2">
-        <v>445</v>
+        <v>460</v>
       </c>
       <c r="C56" s="2"/>
       <c r="D56" t="s" s="2">
@@ -8332,10 +8407,10 @@
     </row>
     <row r="57" hidden="true">
       <c r="A57" t="s" s="2">
-        <v>446</v>
+        <v>461</v>
       </c>
       <c r="B57" t="s" s="2">
-        <v>446</v>
+        <v>461</v>
       </c>
       <c r="C57" s="2"/>
       <c r="D57" t="s" s="2">
@@ -8405,16 +8480,16 @@
         <v>78</v>
       </c>
       <c r="AB57" t="s" s="2">
-        <v>78</v>
+        <v>113</v>
       </c>
       <c r="AC57" t="s" s="2">
-        <v>78</v>
+        <v>114</v>
       </c>
       <c r="AD57" t="s" s="2">
         <v>78</v>
       </c>
       <c r="AE57" t="s" s="2">
-        <v>78</v>
+        <v>115</v>
       </c>
       <c r="AF57" t="s" s="2">
         <v>116</v>
@@ -8446,14 +8521,14 @@
     </row>
     <row r="58" hidden="true">
       <c r="A58" t="s" s="2">
-        <v>447</v>
+        <v>462</v>
       </c>
       <c r="B58" t="s" s="2">
-        <v>447</v>
+        <v>462</v>
       </c>
       <c r="C58" s="2"/>
       <c r="D58" t="s" s="2">
-        <v>448</v>
+        <v>463</v>
       </c>
       <c r="E58" s="2"/>
       <c r="F58" t="s" s="2">
@@ -8475,16 +8550,16 @@
         <v>109</v>
       </c>
       <c r="L58" t="s" s="2">
-        <v>449</v>
+        <v>464</v>
       </c>
       <c r="M58" t="s" s="2">
-        <v>450</v>
+        <v>465</v>
       </c>
       <c r="N58" t="s" s="2">
         <v>112</v>
       </c>
       <c r="O58" t="s" s="2">
-        <v>194</v>
+        <v>197</v>
       </c>
       <c r="P58" t="s" s="2">
         <v>78</v>
@@ -8533,7 +8608,7 @@
         <v>78</v>
       </c>
       <c r="AF58" t="s" s="2">
-        <v>451</v>
+        <v>466</v>
       </c>
       <c r="AG58" t="s" s="2">
         <v>79</v>
@@ -8551,7 +8626,7 @@
         <v>78</v>
       </c>
       <c r="AL58" t="s" s="2">
-        <v>187</v>
+        <v>190</v>
       </c>
       <c r="AM58" t="s" s="2">
         <v>78</v>
@@ -8562,10 +8637,10 @@
     </row>
     <row r="59" hidden="true">
       <c r="A59" t="s" s="2">
-        <v>452</v>
+        <v>467</v>
       </c>
       <c r="B59" t="s" s="2">
-        <v>452</v>
+        <v>467</v>
       </c>
       <c r="C59" s="2"/>
       <c r="D59" t="s" s="2">
@@ -8588,17 +8663,17 @@
         <v>78</v>
       </c>
       <c r="K59" t="s" s="2">
-        <v>453</v>
+        <v>468</v>
       </c>
       <c r="L59" t="s" s="2">
-        <v>454</v>
+        <v>469</v>
       </c>
       <c r="M59" t="s" s="2">
-        <v>455</v>
+        <v>470</v>
       </c>
       <c r="N59" s="2"/>
       <c r="O59" t="s" s="2">
-        <v>456</v>
+        <v>471</v>
       </c>
       <c r="P59" t="s" s="2">
         <v>78</v>
@@ -8647,7 +8722,7 @@
         <v>78</v>
       </c>
       <c r="AF59" t="s" s="2">
-        <v>452</v>
+        <v>467</v>
       </c>
       <c r="AG59" t="s" s="2">
         <v>79</v>
@@ -8665,7 +8740,7 @@
         <v>78</v>
       </c>
       <c r="AL59" t="s" s="2">
-        <v>457</v>
+        <v>472</v>
       </c>
       <c r="AM59" t="s" s="2">
         <v>78</v>
@@ -8676,10 +8751,10 @@
     </row>
     <row r="60" hidden="true">
       <c r="A60" t="s" s="2">
-        <v>458</v>
+        <v>473</v>
       </c>
       <c r="B60" t="s" s="2">
-        <v>458</v>
+        <v>473</v>
       </c>
       <c r="C60" s="2"/>
       <c r="D60" t="s" s="2">
@@ -8702,19 +8777,19 @@
         <v>78</v>
       </c>
       <c r="K60" t="s" s="2">
-        <v>348</v>
+        <v>359</v>
       </c>
       <c r="L60" t="s" s="2">
-        <v>459</v>
+        <v>474</v>
       </c>
       <c r="M60" t="s" s="2">
-        <v>460</v>
+        <v>475</v>
       </c>
       <c r="N60" t="s" s="2">
-        <v>461</v>
+        <v>476</v>
       </c>
       <c r="O60" t="s" s="2">
-        <v>462</v>
+        <v>477</v>
       </c>
       <c r="P60" t="s" s="2">
         <v>78</v>
@@ -8763,7 +8838,7 @@
         <v>78</v>
       </c>
       <c r="AF60" t="s" s="2">
-        <v>458</v>
+        <v>473</v>
       </c>
       <c r="AG60" t="s" s="2">
         <v>79</v>
@@ -8772,30 +8847,30 @@
         <v>88</v>
       </c>
       <c r="AI60" t="s" s="2">
-        <v>78</v>
+        <v>150</v>
       </c>
       <c r="AJ60" t="s" s="2">
-        <v>100</v>
+        <v>363</v>
       </c>
       <c r="AK60" t="s" s="2">
         <v>78</v>
       </c>
       <c r="AL60" t="s" s="2">
-        <v>463</v>
+        <v>478</v>
       </c>
       <c r="AM60" t="s" s="2">
         <v>78</v>
       </c>
       <c r="AN60" t="s" s="2">
-        <v>78</v>
+        <v>367</v>
       </c>
     </row>
     <row r="61" hidden="true">
       <c r="A61" t="s" s="2">
-        <v>464</v>
+        <v>479</v>
       </c>
       <c r="B61" t="s" s="2">
-        <v>464</v>
+        <v>479</v>
       </c>
       <c r="C61" s="2"/>
       <c r="D61" t="s" s="2">
@@ -8818,15 +8893,17 @@
         <v>78</v>
       </c>
       <c r="K61" t="s" s="2">
-        <v>465</v>
+        <v>480</v>
       </c>
       <c r="L61" t="s" s="2">
-        <v>466</v>
+        <v>481</v>
       </c>
       <c r="M61" t="s" s="2">
-        <v>467</v>
-      </c>
-      <c r="N61" s="2"/>
+        <v>482</v>
+      </c>
+      <c r="N61" t="s" s="2">
+        <v>233</v>
+      </c>
       <c r="O61" s="2"/>
       <c r="P61" t="s" s="2">
         <v>78</v>
@@ -8875,7 +8952,7 @@
         <v>78</v>
       </c>
       <c r="AF61" t="s" s="2">
-        <v>464</v>
+        <v>479</v>
       </c>
       <c r="AG61" t="s" s="2">
         <v>79</v>
@@ -8884,16 +8961,16 @@
         <v>80</v>
       </c>
       <c r="AI61" t="s" s="2">
-        <v>78</v>
+        <v>150</v>
       </c>
       <c r="AJ61" t="s" s="2">
-        <v>100</v>
+        <v>234</v>
       </c>
       <c r="AK61" t="s" s="2">
         <v>78</v>
       </c>
       <c r="AL61" t="s" s="2">
-        <v>468</v>
+        <v>483</v>
       </c>
       <c r="AM61" t="s" s="2">
         <v>78</v>
@@ -8904,14 +8981,14 @@
     </row>
     <row r="62">
       <c r="A62" t="s" s="2">
-        <v>469</v>
+        <v>484</v>
       </c>
       <c r="B62" t="s" s="2">
-        <v>469</v>
+        <v>484</v>
       </c>
       <c r="C62" s="2"/>
       <c r="D62" t="s" s="2">
-        <v>470</v>
+        <v>485</v>
       </c>
       <c r="E62" s="2"/>
       <c r="F62" t="s" s="2">
@@ -8930,17 +9007,17 @@
         <v>78</v>
       </c>
       <c r="K62" t="s" s="2">
-        <v>440</v>
+        <v>455</v>
       </c>
       <c r="L62" t="s" s="2">
-        <v>471</v>
+        <v>486</v>
       </c>
       <c r="M62" t="s" s="2">
-        <v>472</v>
+        <v>487</v>
       </c>
       <c r="N62" s="2"/>
       <c r="O62" t="s" s="2">
-        <v>473</v>
+        <v>488</v>
       </c>
       <c r="P62" t="s" s="2">
         <v>78</v>
@@ -8989,7 +9066,7 @@
         <v>78</v>
       </c>
       <c r="AF62" t="s" s="2">
-        <v>469</v>
+        <v>484</v>
       </c>
       <c r="AG62" t="s" s="2">
         <v>79</v>
@@ -8998,7 +9075,7 @@
         <v>80</v>
       </c>
       <c r="AI62" t="s" s="2">
-        <v>78</v>
+        <v>150</v>
       </c>
       <c r="AJ62" t="s" s="2">
         <v>100</v>
@@ -9007,7 +9084,7 @@
         <v>78</v>
       </c>
       <c r="AL62" t="s" s="2">
-        <v>474</v>
+        <v>489</v>
       </c>
       <c r="AM62" t="s" s="2">
         <v>78</v>
@@ -9018,10 +9095,10 @@
     </row>
     <row r="63" hidden="true">
       <c r="A63" t="s" s="2">
-        <v>475</v>
+        <v>490</v>
       </c>
       <c r="B63" t="s" s="2">
-        <v>475</v>
+        <v>490</v>
       </c>
       <c r="C63" s="2"/>
       <c r="D63" t="s" s="2">
@@ -9130,10 +9207,10 @@
     </row>
     <row r="64" hidden="true">
       <c r="A64" t="s" s="2">
-        <v>476</v>
+        <v>491</v>
       </c>
       <c r="B64" t="s" s="2">
-        <v>476</v>
+        <v>491</v>
       </c>
       <c r="C64" s="2"/>
       <c r="D64" t="s" s="2">
@@ -9203,16 +9280,16 @@
         <v>78</v>
       </c>
       <c r="AB64" t="s" s="2">
-        <v>78</v>
+        <v>113</v>
       </c>
       <c r="AC64" t="s" s="2">
-        <v>78</v>
+        <v>114</v>
       </c>
       <c r="AD64" t="s" s="2">
         <v>78</v>
       </c>
       <c r="AE64" t="s" s="2">
-        <v>78</v>
+        <v>115</v>
       </c>
       <c r="AF64" t="s" s="2">
         <v>116</v>
@@ -9244,14 +9321,14 @@
     </row>
     <row r="65" hidden="true">
       <c r="A65" t="s" s="2">
-        <v>477</v>
+        <v>492</v>
       </c>
       <c r="B65" t="s" s="2">
-        <v>477</v>
+        <v>492</v>
       </c>
       <c r="C65" s="2"/>
       <c r="D65" t="s" s="2">
-        <v>448</v>
+        <v>463</v>
       </c>
       <c r="E65" s="2"/>
       <c r="F65" t="s" s="2">
@@ -9273,16 +9350,16 @@
         <v>109</v>
       </c>
       <c r="L65" t="s" s="2">
-        <v>449</v>
+        <v>464</v>
       </c>
       <c r="M65" t="s" s="2">
-        <v>450</v>
+        <v>465</v>
       </c>
       <c r="N65" t="s" s="2">
         <v>112</v>
       </c>
       <c r="O65" t="s" s="2">
-        <v>194</v>
+        <v>197</v>
       </c>
       <c r="P65" t="s" s="2">
         <v>78</v>
@@ -9331,7 +9408,7 @@
         <v>78</v>
       </c>
       <c r="AF65" t="s" s="2">
-        <v>451</v>
+        <v>466</v>
       </c>
       <c r="AG65" t="s" s="2">
         <v>79</v>
@@ -9349,7 +9426,7 @@
         <v>78</v>
       </c>
       <c r="AL65" t="s" s="2">
-        <v>187</v>
+        <v>190</v>
       </c>
       <c r="AM65" t="s" s="2">
         <v>78</v>
@@ -9360,14 +9437,14 @@
     </row>
     <row r="66" hidden="true">
       <c r="A66" t="s" s="2">
-        <v>478</v>
+        <v>493</v>
       </c>
       <c r="B66" t="s" s="2">
-        <v>478</v>
+        <v>493</v>
       </c>
       <c r="C66" s="2"/>
       <c r="D66" t="s" s="2">
-        <v>479</v>
+        <v>494</v>
       </c>
       <c r="E66" s="2"/>
       <c r="F66" t="s" s="2">
@@ -9386,19 +9463,19 @@
         <v>78</v>
       </c>
       <c r="K66" t="s" s="2">
-        <v>253</v>
+        <v>261</v>
       </c>
       <c r="L66" t="s" s="2">
-        <v>480</v>
+        <v>495</v>
       </c>
       <c r="M66" t="s" s="2">
-        <v>481</v>
+        <v>496</v>
       </c>
       <c r="N66" t="s" s="2">
-        <v>482</v>
+        <v>497</v>
       </c>
       <c r="O66" t="s" s="2">
-        <v>483</v>
+        <v>498</v>
       </c>
       <c r="P66" t="s" s="2">
         <v>78</v>
@@ -9423,10 +9500,10 @@
         <v>78</v>
       </c>
       <c r="X66" t="s" s="2">
-        <v>154</v>
+        <v>157</v>
       </c>
       <c r="Y66" t="s" s="2">
-        <v>484</v>
+        <v>499</v>
       </c>
       <c r="Z66" t="s" s="2">
         <v>78</v>
@@ -9447,7 +9524,7 @@
         <v>78</v>
       </c>
       <c r="AF66" t="s" s="2">
-        <v>478</v>
+        <v>493</v>
       </c>
       <c r="AG66" t="s" s="2">
         <v>88</v>
@@ -9456,7 +9533,7 @@
         <v>88</v>
       </c>
       <c r="AI66" t="s" s="2">
-        <v>78</v>
+        <v>150</v>
       </c>
       <c r="AJ66" t="s" s="2">
         <v>100</v>
@@ -9465,21 +9542,21 @@
         <v>78</v>
       </c>
       <c r="AL66" t="s" s="2">
-        <v>474</v>
+        <v>489</v>
       </c>
       <c r="AM66" t="s" s="2">
         <v>78</v>
       </c>
       <c r="AN66" t="s" s="2">
-        <v>78</v>
+        <v>267</v>
       </c>
     </row>
     <row r="67" hidden="true">
       <c r="A67" t="s" s="2">
-        <v>485</v>
+        <v>500</v>
       </c>
       <c r="B67" t="s" s="2">
-        <v>485</v>
+        <v>500</v>
       </c>
       <c r="C67" s="2"/>
       <c r="D67" t="s" s="2">
@@ -9502,13 +9579,13 @@
         <v>78</v>
       </c>
       <c r="K67" t="s" s="2">
-        <v>486</v>
+        <v>501</v>
       </c>
       <c r="L67" t="s" s="2">
-        <v>487</v>
+        <v>502</v>
       </c>
       <c r="M67" t="s" s="2">
-        <v>488</v>
+        <v>503</v>
       </c>
       <c r="N67" s="2"/>
       <c r="O67" s="2"/>
@@ -9559,7 +9636,7 @@
         <v>78</v>
       </c>
       <c r="AF67" t="s" s="2">
-        <v>485</v>
+        <v>500</v>
       </c>
       <c r="AG67" t="s" s="2">
         <v>88</v>
@@ -9568,7 +9645,7 @@
         <v>88</v>
       </c>
       <c r="AI67" t="s" s="2">
-        <v>78</v>
+        <v>150</v>
       </c>
       <c r="AJ67" t="s" s="2">
         <v>100</v>
@@ -9577,7 +9654,7 @@
         <v>78</v>
       </c>
       <c r="AL67" t="s" s="2">
-        <v>474</v>
+        <v>489</v>
       </c>
       <c r="AM67" t="s" s="2">
         <v>78</v>
@@ -9588,10 +9665,10 @@
     </row>
     <row r="68">
       <c r="A68" t="s" s="2">
-        <v>489</v>
+        <v>504</v>
       </c>
       <c r="B68" t="s" s="2">
-        <v>489</v>
+        <v>504</v>
       </c>
       <c r="C68" s="2"/>
       <c r="D68" t="s" s="2">
@@ -9614,17 +9691,17 @@
         <v>78</v>
       </c>
       <c r="K68" t="s" s="2">
-        <v>440</v>
+        <v>455</v>
       </c>
       <c r="L68" t="s" s="2">
-        <v>490</v>
+        <v>505</v>
       </c>
       <c r="M68" t="s" s="2">
-        <v>491</v>
+        <v>506</v>
       </c>
       <c r="N68" s="2"/>
       <c r="O68" t="s" s="2">
-        <v>492</v>
+        <v>507</v>
       </c>
       <c r="P68" t="s" s="2">
         <v>78</v>
@@ -9673,7 +9750,7 @@
         <v>78</v>
       </c>
       <c r="AF68" t="s" s="2">
-        <v>489</v>
+        <v>504</v>
       </c>
       <c r="AG68" t="s" s="2">
         <v>79</v>
@@ -9682,7 +9759,7 @@
         <v>80</v>
       </c>
       <c r="AI68" t="s" s="2">
-        <v>78</v>
+        <v>150</v>
       </c>
       <c r="AJ68" t="s" s="2">
         <v>100</v>
@@ -9691,7 +9768,7 @@
         <v>78</v>
       </c>
       <c r="AL68" t="s" s="2">
-        <v>474</v>
+        <v>489</v>
       </c>
       <c r="AM68" t="s" s="2">
         <v>78</v>
@@ -9702,10 +9779,10 @@
     </row>
     <row r="69" hidden="true">
       <c r="A69" t="s" s="2">
-        <v>493</v>
+        <v>508</v>
       </c>
       <c r="B69" t="s" s="2">
-        <v>493</v>
+        <v>508</v>
       </c>
       <c r="C69" s="2"/>
       <c r="D69" t="s" s="2">
@@ -9814,10 +9891,10 @@
     </row>
     <row r="70" hidden="true">
       <c r="A70" t="s" s="2">
-        <v>494</v>
+        <v>509</v>
       </c>
       <c r="B70" t="s" s="2">
-        <v>494</v>
+        <v>509</v>
       </c>
       <c r="C70" s="2"/>
       <c r="D70" t="s" s="2">
@@ -9887,16 +9964,16 @@
         <v>78</v>
       </c>
       <c r="AB70" t="s" s="2">
-        <v>78</v>
+        <v>113</v>
       </c>
       <c r="AC70" t="s" s="2">
-        <v>78</v>
+        <v>114</v>
       </c>
       <c r="AD70" t="s" s="2">
         <v>78</v>
       </c>
       <c r="AE70" t="s" s="2">
-        <v>78</v>
+        <v>115</v>
       </c>
       <c r="AF70" t="s" s="2">
         <v>116</v>
@@ -9928,14 +10005,14 @@
     </row>
     <row r="71" hidden="true">
       <c r="A71" t="s" s="2">
-        <v>495</v>
+        <v>510</v>
       </c>
       <c r="B71" t="s" s="2">
-        <v>495</v>
+        <v>510</v>
       </c>
       <c r="C71" s="2"/>
       <c r="D71" t="s" s="2">
-        <v>448</v>
+        <v>463</v>
       </c>
       <c r="E71" s="2"/>
       <c r="F71" t="s" s="2">
@@ -9957,16 +10034,16 @@
         <v>109</v>
       </c>
       <c r="L71" t="s" s="2">
-        <v>449</v>
+        <v>464</v>
       </c>
       <c r="M71" t="s" s="2">
-        <v>450</v>
+        <v>465</v>
       </c>
       <c r="N71" t="s" s="2">
         <v>112</v>
       </c>
       <c r="O71" t="s" s="2">
-        <v>194</v>
+        <v>197</v>
       </c>
       <c r="P71" t="s" s="2">
         <v>78</v>
@@ -10015,7 +10092,7 @@
         <v>78</v>
       </c>
       <c r="AF71" t="s" s="2">
-        <v>451</v>
+        <v>466</v>
       </c>
       <c r="AG71" t="s" s="2">
         <v>79</v>
@@ -10033,7 +10110,7 @@
         <v>78</v>
       </c>
       <c r="AL71" t="s" s="2">
-        <v>187</v>
+        <v>190</v>
       </c>
       <c r="AM71" t="s" s="2">
         <v>78</v>
@@ -10044,14 +10121,14 @@
     </row>
     <row r="72" hidden="true">
       <c r="A72" t="s" s="2">
-        <v>496</v>
+        <v>511</v>
       </c>
       <c r="B72" t="s" s="2">
-        <v>496</v>
+        <v>511</v>
       </c>
       <c r="C72" s="2"/>
       <c r="D72" t="s" s="2">
-        <v>479</v>
+        <v>494</v>
       </c>
       <c r="E72" s="2"/>
       <c r="F72" t="s" s="2">
@@ -10070,17 +10147,19 @@
         <v>78</v>
       </c>
       <c r="K72" t="s" s="2">
-        <v>253</v>
+        <v>261</v>
       </c>
       <c r="L72" t="s" s="2">
-        <v>497</v>
+        <v>512</v>
       </c>
       <c r="M72" t="s" s="2">
-        <v>498</v>
-      </c>
-      <c r="N72" s="2"/>
+        <v>513</v>
+      </c>
+      <c r="N72" t="s" s="2">
+        <v>271</v>
+      </c>
       <c r="O72" t="s" s="2">
-        <v>499</v>
+        <v>514</v>
       </c>
       <c r="P72" t="s" s="2">
         <v>78</v>
@@ -10105,10 +10184,10 @@
         <v>78</v>
       </c>
       <c r="X72" t="s" s="2">
-        <v>154</v>
+        <v>157</v>
       </c>
       <c r="Y72" t="s" s="2">
-        <v>500</v>
+        <v>515</v>
       </c>
       <c r="Z72" t="s" s="2">
         <v>78</v>
@@ -10129,7 +10208,7 @@
         <v>78</v>
       </c>
       <c r="AF72" t="s" s="2">
-        <v>496</v>
+        <v>511</v>
       </c>
       <c r="AG72" t="s" s="2">
         <v>88</v>
@@ -10138,7 +10217,7 @@
         <v>88</v>
       </c>
       <c r="AI72" t="s" s="2">
-        <v>78</v>
+        <v>150</v>
       </c>
       <c r="AJ72" t="s" s="2">
         <v>100</v>
@@ -10147,21 +10226,21 @@
         <v>78</v>
       </c>
       <c r="AL72" t="s" s="2">
-        <v>474</v>
+        <v>489</v>
       </c>
       <c r="AM72" t="s" s="2">
         <v>78</v>
       </c>
       <c r="AN72" t="s" s="2">
-        <v>78</v>
+        <v>267</v>
       </c>
     </row>
     <row r="73" hidden="true">
       <c r="A73" t="s" s="2">
-        <v>501</v>
+        <v>516</v>
       </c>
       <c r="B73" t="s" s="2">
-        <v>501</v>
+        <v>516</v>
       </c>
       <c r="C73" s="2"/>
       <c r="D73" t="s" s="2">
@@ -10184,17 +10263,17 @@
         <v>78</v>
       </c>
       <c r="K73" t="s" s="2">
-        <v>486</v>
+        <v>501</v>
       </c>
       <c r="L73" t="s" s="2">
-        <v>502</v>
+        <v>517</v>
       </c>
       <c r="M73" t="s" s="2">
-        <v>503</v>
+        <v>518</v>
       </c>
       <c r="N73" s="2"/>
       <c r="O73" t="s" s="2">
-        <v>504</v>
+        <v>519</v>
       </c>
       <c r="P73" t="s" s="2">
         <v>78</v>
@@ -10243,7 +10322,7 @@
         <v>78</v>
       </c>
       <c r="AF73" t="s" s="2">
-        <v>501</v>
+        <v>516</v>
       </c>
       <c r="AG73" t="s" s="2">
         <v>88</v>
@@ -10252,7 +10331,7 @@
         <v>88</v>
       </c>
       <c r="AI73" t="s" s="2">
-        <v>78</v>
+        <v>150</v>
       </c>
       <c r="AJ73" t="s" s="2">
         <v>100</v>
@@ -10261,7 +10340,7 @@
         <v>78</v>
       </c>
       <c r="AL73" t="s" s="2">
-        <v>474</v>
+        <v>489</v>
       </c>
       <c r="AM73" t="s" s="2">
         <v>78</v>
